--- a/automation/reports/Excel/Selenium_E2E_Test_Report.xlsx
+++ b/automation/reports/Excel/Selenium_E2E_Test_Report.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05 19:39:58</t>
+          <t>2026-10-05 21:16:31</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>672.21s</t>
+          <t>671.03s</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="H2" s="11" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="H3" s="14" t="n">
-        <v>0.41</v>
+        <v>1.83</v>
       </c>
       <c r="I3" s="14" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>1.58</v>
+        <v>2.37</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="H5" s="14" t="n">
-        <v>2.49</v>
+        <v>1.12</v>
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.41</v>
+        <v>1.26</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="H7" s="14" t="n">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>2.43</v>
+        <v>0.76</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="H9" s="14" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>1.21</v>
+        <v>2.16</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="H11" s="14" t="n">
-        <v>0.6</v>
+        <v>1.89</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.86</v>
+        <v>1.56</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="H13" s="14" t="n">
-        <v>0.95</v>
+        <v>1.16</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="H15" s="14" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="H17" s="14" t="n">
-        <v>1.69</v>
+        <v>0.64</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1.05</v>
+        <v>0.64</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="H19" s="14" t="n">
-        <v>2.42</v>
+        <v>0.46</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="H21" s="14" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>1.51</v>
+        <v>0.41</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="H23" s="14" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.62</v>
+        <v>2.26</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="H25" s="14" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="H27" s="14" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="H29" s="14" t="n">
-        <v>2.13</v>
+        <v>0.65</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>2.25</v>
+        <v>1.13</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="H31" s="14" t="n">
-        <v>0.79</v>
+        <v>1.92</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="H33" s="14" t="n">
-        <v>2.1</v>
+        <v>0.42</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>0.92</v>
+        <v>1.93</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="H35" s="14" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="H37" s="14" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="H39" s="14" t="n">
-        <v>2.47</v>
+        <v>1.91</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>1.44</v>
+        <v>0.89</v>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="H41" s="14" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.86</v>
+        <v>1.48</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="H43" s="14" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="H45" s="14" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.61</v>
+        <v>2.27</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="H47" s="14" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>1.29</v>
+        <v>0.48</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="H49" s="14" t="n">
-        <v>1.53</v>
+        <v>0.48</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="H51" s="14" t="n">
-        <v>1.04</v>
+        <v>0.46</v>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="H53" s="14" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>1.45</v>
+        <v>0.49</v>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         </is>
       </c>
       <c r="H55" s="14" t="n">
-        <v>1.81</v>
+        <v>0.95</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>0.63</v>
+        <v>2.31</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="H57" s="14" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>0.73</v>
+        <v>2.06</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="H59" s="14" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="H61" s="14" t="n">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>1.06</v>
+        <v>2.42</v>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="H63" s="14" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>1.28</v>
+        <v>2.49</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="H65" s="14" t="n">
-        <v>2.38</v>
+        <v>1.49</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>2.48</v>
+        <v>0.66</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="H67" s="14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="H69" s="14" t="n">
-        <v>1.2</v>
+        <v>2.19</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>2.19</v>
+        <v>0.89</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="H71" s="14" t="n">
-        <v>0.85</v>
+        <v>2.24</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>2.46</v>
+        <v>1.08</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="H73" s="14" t="n">
-        <v>0.63</v>
+        <v>1.77</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="H75" s="14" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="H77" s="14" t="n">
-        <v>0.7</v>
+        <v>0.41</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>2.29</v>
+        <v>0.58</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="H79" s="14" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="H81" s="14" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="H83" s="14" t="n">
-        <v>0.42</v>
+        <v>2.41</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>0.57</v>
+        <v>1.4</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="H85" s="14" t="n">
-        <v>2.2</v>
+        <v>0.87</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="H87" s="14" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0.87</v>
+        <v>1.7</v>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="H89" s="14" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0.62</v>
+        <v>1.41</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="H91" s="14" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>2.48</v>
+        <v>1.06</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="H93" s="14" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="H95" s="14" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="H97" s="14" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.59</v>
+        <v>1.73</v>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="H99" s="14" t="n">
-        <v>2.21</v>
+        <v>0.45</v>
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0.47</v>
+        <v>2.23</v>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="H101" s="14" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0.64</v>
+        <v>1.4</v>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         </is>
       </c>
       <c r="H103" s="14" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H104" s="11" t="n">
-        <v>1.65</v>
+        <v>0.89</v>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="H105" s="14" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="H106" s="11" t="n">
-        <v>2.3</v>
+        <v>0.41</v>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="H107" s="14" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="H108" s="11" t="n">
-        <v>0.54</v>
+        <v>1.8</v>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="H109" s="14" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="H110" s="11" t="n">
-        <v>1.24</v>
+        <v>0.4</v>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H111" s="14" t="n">
-        <v>1.53</v>
+        <v>0.58</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="H112" s="11" t="n">
-        <v>0.64</v>
+        <v>1.2</v>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="H113" s="14" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="H114" s="11" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="H115" s="14" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="H116" s="11" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="H117" s="14" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="H118" s="11" t="n">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="H119" s="14" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="H120" s="11" t="n">
-        <v>1.89</v>
+        <v>0.55</v>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="H121" s="14" t="n">
-        <v>0.53</v>
+        <v>1.38</v>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="H122" s="11" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="H123" s="14" t="n">
-        <v>0.62</v>
+        <v>1.24</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="H124" s="11" t="n">
-        <v>0.48</v>
+        <v>1.56</v>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="H125" s="14" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="H126" s="11" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="H127" s="14" t="n">
-        <v>1.6</v>
+        <v>2.39</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="H128" s="11" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="H129" s="14" t="n">
-        <v>2.39</v>
+        <v>0.82</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         </is>
       </c>
       <c r="H130" s="11" t="n">
-        <v>0.96</v>
+        <v>1.65</v>
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="H131" s="14" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="H132" s="11" t="n">
-        <v>0.41</v>
+        <v>1.85</v>
       </c>
       <c r="I132" s="11" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="H133" s="14" t="n">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="H134" s="11" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="I134" s="11" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="H135" s="14" t="n">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="I135" s="14" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="H136" s="11" t="n">
-        <v>2.41</v>
+        <v>0.75</v>
       </c>
       <c r="I136" s="11" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="H137" s="14" t="n">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="H138" s="11" t="n">
-        <v>2.26</v>
+        <v>0.54</v>
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="H139" s="14" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="H140" s="11" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="H141" s="14" t="n">
-        <v>0.62</v>
+        <v>2.37</v>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         </is>
       </c>
       <c r="H142" s="11" t="n">
-        <v>2.21</v>
+        <v>1.05</v>
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         </is>
       </c>
       <c r="H143" s="14" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="I143" s="14" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="H144" s="11" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="H145" s="14" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="I145" s="14" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="H146" s="11" t="n">
-        <v>2.01</v>
+        <v>0.74</v>
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="H147" s="14" t="n">
-        <v>0.43</v>
+        <v>2.09</v>
       </c>
       <c r="I147" s="14" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="H148" s="11" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="H149" s="14" t="n">
-        <v>1.31</v>
+        <v>0.41</v>
       </c>
       <c r="I149" s="14" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="H150" s="11" t="n">
-        <v>0.84</v>
+        <v>1.58</v>
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="H151" s="14" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="H152" s="11" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="I152" s="11" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="H153" s="14" t="n">
-        <v>2.29</v>
+        <v>1.25</v>
       </c>
       <c r="I153" s="14" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="H154" s="11" t="n">
-        <v>1.45</v>
+        <v>0.66</v>
       </c>
       <c r="I154" s="11" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="H155" s="14" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="I155" s="14" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="H156" s="11" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="I156" s="11" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         </is>
       </c>
       <c r="H157" s="14" t="n">
-        <v>2.36</v>
+        <v>1.16</v>
       </c>
       <c r="I157" s="14" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="H158" s="11" t="n">
-        <v>1.17</v>
+        <v>0.99</v>
       </c>
       <c r="I158" s="11" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         </is>
       </c>
       <c r="H159" s="14" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="I159" s="14" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="H160" s="11" t="n">
-        <v>1.15</v>
+        <v>0.88</v>
       </c>
       <c r="I160" s="11" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         </is>
       </c>
       <c r="H161" s="14" t="n">
-        <v>0.78</v>
+        <v>1.18</v>
       </c>
       <c r="I161" s="14" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="H162" s="11" t="n">
-        <v>0.99</v>
+        <v>2.02</v>
       </c>
       <c r="I162" s="11" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="H163" s="14" t="n">
-        <v>0.53</v>
+        <v>1.3</v>
       </c>
       <c r="I163" s="14" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="H164" s="11" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="I164" s="11" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="H165" s="14" t="n">
-        <v>1.96</v>
+        <v>1.19</v>
       </c>
       <c r="I165" s="14" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="H166" s="11" t="n">
-        <v>1.13</v>
+        <v>2.09</v>
       </c>
       <c r="I166" s="11" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         </is>
       </c>
       <c r="H167" s="14" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="I167" s="14" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         </is>
       </c>
       <c r="H168" s="11" t="n">
-        <v>1.65</v>
+        <v>0.54</v>
       </c>
       <c r="I168" s="11" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="H169" s="14" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="I169" s="14" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="H170" s="11" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="I170" s="11" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         </is>
       </c>
       <c r="H171" s="14" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="I171" s="14" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="H172" s="11" t="n">
-        <v>0.51</v>
+        <v>1.97</v>
       </c>
       <c r="I172" s="11" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="H173" s="14" t="n">
-        <v>1.1</v>
+        <v>2.29</v>
       </c>
       <c r="I173" s="14" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="H174" s="11" t="n">
-        <v>1.09</v>
+        <v>0.45</v>
       </c>
       <c r="I174" s="11" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="H175" s="14" t="n">
-        <v>0.66</v>
+        <v>1.31</v>
       </c>
       <c r="I175" s="14" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="H176" s="11" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="I176" s="11" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="H177" s="14" t="n">
-        <v>1.08</v>
+        <v>1.95</v>
       </c>
       <c r="I177" s="14" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="H178" s="11" t="n">
-        <v>1.96</v>
+        <v>1.15</v>
       </c>
       <c r="I178" s="11" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         </is>
       </c>
       <c r="H179" s="14" t="n">
-        <v>2.38</v>
+        <v>0.72</v>
       </c>
       <c r="I179" s="14" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         </is>
       </c>
       <c r="H180" s="11" t="n">
-        <v>1.29</v>
+        <v>1.99</v>
       </c>
       <c r="I180" s="11" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="H181" s="14" t="n">
-        <v>0.96</v>
+        <v>1.83</v>
       </c>
       <c r="I181" s="14" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="H182" s="11" t="n">
-        <v>2.03</v>
+        <v>1.42</v>
       </c>
       <c r="I182" s="11" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         </is>
       </c>
       <c r="H183" s="14" t="n">
-        <v>0.63</v>
+        <v>1.62</v>
       </c>
       <c r="I183" s="14" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="H184" s="11" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="I184" s="11" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         </is>
       </c>
       <c r="H185" s="14" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="I185" s="14" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="H186" s="11" t="n">
-        <v>0.89</v>
+        <v>2.4</v>
       </c>
       <c r="I186" s="11" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         </is>
       </c>
       <c r="H187" s="14" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="I187" s="14" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         </is>
       </c>
       <c r="H188" s="11" t="n">
-        <v>0.97</v>
+        <v>1.84</v>
       </c>
       <c r="I188" s="11" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="H189" s="14" t="n">
-        <v>1.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I189" s="14" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         </is>
       </c>
       <c r="H190" s="11" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="I190" s="11" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="H191" s="14" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="I191" s="14" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="H192" s="11" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="I192" s="11" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         </is>
       </c>
       <c r="H193" s="14" t="n">
-        <v>2.45</v>
+        <v>0.95</v>
       </c>
       <c r="I193" s="14" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="H194" s="11" t="n">
-        <v>1.17</v>
+        <v>2.26</v>
       </c>
       <c r="I194" s="11" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         </is>
       </c>
       <c r="H195" s="14" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="I195" s="14" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="H196" s="11" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="I196" s="11" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         </is>
       </c>
       <c r="H197" s="14" t="n">
-        <v>1.39</v>
+        <v>2.49</v>
       </c>
       <c r="I197" s="14" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="H198" s="11" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="I198" s="11" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="H199" s="14" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="I199" s="14" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         </is>
       </c>
       <c r="H200" s="11" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="I200" s="11" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         </is>
       </c>
       <c r="H201" s="14" t="n">
-        <v>0.61</v>
+        <v>1.94</v>
       </c>
       <c r="I201" s="14" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="H202" s="11" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="I202" s="11" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         </is>
       </c>
       <c r="H203" s="14" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="I203" s="14" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="H204" s="11" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="I204" s="11" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         </is>
       </c>
       <c r="H205" s="14" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="I205" s="14" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         </is>
       </c>
       <c r="H206" s="11" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="I206" s="11" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="H207" s="14" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="I207" s="14" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         </is>
       </c>
       <c r="H208" s="11" t="n">
-        <v>0.8</v>
+        <v>2.38</v>
       </c>
       <c r="I208" s="11" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="H209" s="14" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="I209" s="14" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         </is>
       </c>
       <c r="H210" s="11" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="I210" s="11" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="H211" s="14" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="I211" s="14" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         </is>
       </c>
       <c r="H212" s="11" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="I212" s="11" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         </is>
       </c>
       <c r="H213" s="14" t="n">
-        <v>0.44</v>
+        <v>1.86</v>
       </c>
       <c r="I213" s="14" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         </is>
       </c>
       <c r="H214" s="11" t="n">
-        <v>0.87</v>
+        <v>2.16</v>
       </c>
       <c r="I214" s="11" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
         </is>
       </c>
       <c r="H215" s="14" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="I215" s="14" t="inlineStr">
         <is>
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="H216" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="I216" s="11" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         </is>
       </c>
       <c r="H217" s="14" t="n">
-        <v>0.65</v>
+        <v>2.18</v>
       </c>
       <c r="I217" s="14" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         </is>
       </c>
       <c r="H218" s="11" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="I218" s="11" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="H219" s="14" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="I219" s="14" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
         </is>
       </c>
       <c r="H220" s="11" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="I220" s="11" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="H221" s="14" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="I221" s="14" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         </is>
       </c>
       <c r="H222" s="11" t="n">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I222" s="11" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         </is>
       </c>
       <c r="H223" s="14" t="n">
-        <v>2.34</v>
+        <v>1.28</v>
       </c>
       <c r="I223" s="14" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         </is>
       </c>
       <c r="H224" s="11" t="n">
-        <v>1.77</v>
+        <v>0.59</v>
       </c>
       <c r="I224" s="11" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="H225" s="14" t="n">
-        <v>1.05</v>
+        <v>2.27</v>
       </c>
       <c r="I225" s="14" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="H226" s="11" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="I226" s="11" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="H227" s="14" t="n">
-        <v>2.17</v>
+        <v>0.95</v>
       </c>
       <c r="I227" s="14" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="H228" s="11" t="n">
-        <v>0.92</v>
+        <v>1.43</v>
       </c>
       <c r="I228" s="11" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="H229" s="14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I229" s="14" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="H230" s="11" t="n">
-        <v>1.41</v>
+        <v>0.91</v>
       </c>
       <c r="I230" s="11" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="H231" s="14" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="I231" s="14" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         </is>
       </c>
       <c r="H232" s="11" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="I232" s="11" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="H233" s="14" t="n">
-        <v>1.89</v>
+        <v>1.02</v>
       </c>
       <c r="I233" s="14" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         </is>
       </c>
       <c r="H234" s="11" t="n">
-        <v>0.7</v>
+        <v>1.87</v>
       </c>
       <c r="I234" s="11" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         </is>
       </c>
       <c r="H235" s="14" t="n">
-        <v>1.33</v>
+        <v>0.45</v>
       </c>
       <c r="I235" s="14" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="H236" s="11" t="n">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="I236" s="11" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="H237" s="14" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="I237" s="14" t="inlineStr">
         <is>
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="H238" s="11" t="n">
-        <v>1.43</v>
+        <v>2.36</v>
       </c>
       <c r="I238" s="11" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         </is>
       </c>
       <c r="H239" s="14" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="I239" s="14" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="H240" s="11" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="I240" s="11" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         </is>
       </c>
       <c r="H241" s="14" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="I241" s="14" t="inlineStr">
         <is>
@@ -12857,7 +12857,7 @@
         </is>
       </c>
       <c r="H242" s="11" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="I242" s="11" t="inlineStr">
         <is>
@@ -12907,7 +12907,7 @@
         </is>
       </c>
       <c r="H243" s="14" t="n">
-        <v>0.65</v>
+        <v>1.9</v>
       </c>
       <c r="I243" s="14" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         </is>
       </c>
       <c r="H244" s="11" t="n">
-        <v>2.47</v>
+        <v>1.74</v>
       </c>
       <c r="I244" s="11" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         </is>
       </c>
       <c r="H245" s="14" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
       <c r="I245" s="14" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         </is>
       </c>
       <c r="H246" s="11" t="n">
-        <v>1.54</v>
+        <v>0.7</v>
       </c>
       <c r="I246" s="11" t="inlineStr">
         <is>
@@ -13107,7 +13107,7 @@
         </is>
       </c>
       <c r="H247" s="14" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="I247" s="14" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="H248" s="11" t="n">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="I248" s="11" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="H249" s="14" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="I249" s="14" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="H250" s="11" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="I250" s="11" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="H251" s="14" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="I251" s="14" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="H252" s="11" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="I252" s="11" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         </is>
       </c>
       <c r="H253" s="14" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="I253" s="14" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         </is>
       </c>
       <c r="H254" s="11" t="n">
-        <v>1.45</v>
+        <v>0.64</v>
       </c>
       <c r="I254" s="11" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         </is>
       </c>
       <c r="H255" s="14" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="I255" s="14" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="H256" s="11" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="I256" s="11" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="H257" s="14" t="n">
-        <v>2.31</v>
+        <v>1.11</v>
       </c>
       <c r="I257" s="14" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="H258" s="11" t="n">
-        <v>1.05</v>
+        <v>0.59</v>
       </c>
       <c r="I258" s="11" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="H259" s="14" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="I259" s="14" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         </is>
       </c>
       <c r="H260" s="11" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="I260" s="11" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         </is>
       </c>
       <c r="H261" s="14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="I261" s="14" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         </is>
       </c>
       <c r="H262" s="11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="I262" s="11" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         </is>
       </c>
       <c r="H263" s="14" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="I263" s="14" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="H264" s="11" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="I264" s="11" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         </is>
       </c>
       <c r="H265" s="14" t="n">
-        <v>2.12</v>
+        <v>0.46</v>
       </c>
       <c r="I265" s="14" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         </is>
       </c>
       <c r="H266" s="11" t="n">
-        <v>0.66</v>
+        <v>1.89</v>
       </c>
       <c r="I266" s="11" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         </is>
       </c>
       <c r="H267" s="14" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="I267" s="14" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="H268" s="11" t="n">
-        <v>1.69</v>
+        <v>0.92</v>
       </c>
       <c r="I268" s="11" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="H269" s="14" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="I269" s="14" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="H270" s="11" t="n">
-        <v>0.79</v>
+        <v>1.61</v>
       </c>
       <c r="I270" s="11" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="H271" s="14" t="n">
-        <v>1.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I271" s="14" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="H272" s="11" t="n">
-        <v>1.51</v>
+        <v>0.73</v>
       </c>
       <c r="I272" s="11" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="H273" s="14" t="n">
-        <v>0.51</v>
+        <v>2.38</v>
       </c>
       <c r="I273" s="14" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="H274" s="11" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="I274" s="11" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="H275" s="14" t="n">
-        <v>1.68</v>
+        <v>0.45</v>
       </c>
       <c r="I275" s="14" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="H276" s="11" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="I276" s="11" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="H277" s="14" t="n">
-        <v>2.35</v>
+        <v>1.33</v>
       </c>
       <c r="I277" s="14" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="H278" s="11" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="I278" s="11" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="H279" s="14" t="n">
-        <v>1.69</v>
+        <v>0.78</v>
       </c>
       <c r="I279" s="14" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         </is>
       </c>
       <c r="H280" s="11" t="n">
-        <v>0.78</v>
+        <v>1.58</v>
       </c>
       <c r="I280" s="11" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="H281" s="14" t="n">
-        <v>2.11</v>
+        <v>0.68</v>
       </c>
       <c r="I281" s="14" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="H282" s="11" t="n">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="I282" s="11" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="H283" s="14" t="n">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
       <c r="I283" s="14" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="H284" s="11" t="n">
-        <v>2.03</v>
+        <v>1.03</v>
       </c>
       <c r="I284" s="11" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="H285" s="14" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I285" s="14" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="H286" s="11" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="I286" s="11" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         </is>
       </c>
       <c r="H287" s="14" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I287" s="14" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         </is>
       </c>
       <c r="H288" s="11" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="I288" s="11" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         </is>
       </c>
       <c r="H289" s="14" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="I289" s="14" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="H290" s="11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="I290" s="11" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="H291" s="14" t="n">
-        <v>0.52</v>
+        <v>1.65</v>
       </c>
       <c r="I291" s="14" t="inlineStr">
         <is>
@@ -15357,7 +15357,7 @@
         </is>
       </c>
       <c r="H292" s="11" t="n">
-        <v>0.57</v>
+        <v>1.19</v>
       </c>
       <c r="I292" s="11" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         </is>
       </c>
       <c r="H293" s="14" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="I293" s="14" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="H294" s="11" t="n">
-        <v>1.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I294" s="11" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         </is>
       </c>
       <c r="H295" s="14" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="I295" s="14" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         </is>
       </c>
       <c r="H296" s="11" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="I296" s="11" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="H297" s="14" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="I297" s="14" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         </is>
       </c>
       <c r="H298" s="11" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="I298" s="11" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="H299" s="14" t="n">
-        <v>0.74</v>
+        <v>1.56</v>
       </c>
       <c r="I299" s="14" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         </is>
       </c>
       <c r="H300" s="11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I300" s="11" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         </is>
       </c>
       <c r="H301" s="14" t="n">
-        <v>0.97</v>
+        <v>1.26</v>
       </c>
       <c r="I301" s="14" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         </is>
       </c>
       <c r="H302" s="11" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="I302" s="11" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="H303" s="14" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="I303" s="14" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="H304" s="11" t="n">
-        <v>2.05</v>
+        <v>1.16</v>
       </c>
       <c r="I304" s="11" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         </is>
       </c>
       <c r="H305" s="14" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="I305" s="14" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         </is>
       </c>
       <c r="H306" s="11" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="I306" s="11" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         </is>
       </c>
       <c r="H307" s="14" t="n">
-        <v>1.4</v>
+        <v>0.67</v>
       </c>
       <c r="I307" s="14" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         </is>
       </c>
       <c r="H308" s="11" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="I308" s="11" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="H309" s="14" t="n">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="I309" s="14" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         </is>
       </c>
       <c r="H310" s="11" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="I310" s="11" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="H311" s="14" t="n">
-        <v>0.9</v>
+        <v>2.08</v>
       </c>
       <c r="I311" s="14" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="H312" s="11" t="n">
-        <v>1.53</v>
+        <v>0.63</v>
       </c>
       <c r="I312" s="11" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="H313" s="14" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="I313" s="14" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="H314" s="11" t="n">
-        <v>0.49</v>
+        <v>2.05</v>
       </c>
       <c r="I314" s="11" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="H315" s="14" t="n">
-        <v>2.22</v>
+        <v>0.57</v>
       </c>
       <c r="I315" s="14" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="H316" s="11" t="n">
-        <v>1.93</v>
+        <v>0.73</v>
       </c>
       <c r="I316" s="11" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="H317" s="14" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="I317" s="14" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="H318" s="11" t="n">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="I318" s="11" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="H319" s="14" t="n">
-        <v>0.48</v>
+        <v>1.34</v>
       </c>
       <c r="I319" s="14" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="H320" s="11" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="I320" s="11" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="H321" s="14" t="n">
-        <v>2.49</v>
+        <v>0.5</v>
       </c>
       <c r="I321" s="14" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         </is>
       </c>
       <c r="H322" s="11" t="n">
-        <v>1.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I322" s="11" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         </is>
       </c>
       <c r="H323" s="14" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="I323" s="14" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         </is>
       </c>
       <c r="H324" s="11" t="n">
-        <v>2.49</v>
+        <v>1.92</v>
       </c>
       <c r="I324" s="11" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="H325" s="14" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="I325" s="14" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         </is>
       </c>
       <c r="H326" s="11" t="n">
-        <v>1.63</v>
+        <v>0.93</v>
       </c>
       <c r="I326" s="11" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         </is>
       </c>
       <c r="H327" s="14" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="I327" s="14" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         </is>
       </c>
       <c r="H328" s="11" t="n">
-        <v>0.54</v>
+        <v>2.02</v>
       </c>
       <c r="I328" s="11" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         </is>
       </c>
       <c r="H329" s="14" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="I329" s="14" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="H330" s="11" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="I330" s="11" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="H331" s="14" t="n">
-        <v>2.15</v>
+        <v>0.87</v>
       </c>
       <c r="I331" s="14" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="H332" s="11" t="n">
-        <v>0.55</v>
+        <v>1.51</v>
       </c>
       <c r="I332" s="11" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         </is>
       </c>
       <c r="H333" s="14" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="I333" s="14" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="H334" s="11" t="n">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="I334" s="11" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         </is>
       </c>
       <c r="H335" s="14" t="n">
-        <v>2.18</v>
+        <v>1.06</v>
       </c>
       <c r="I335" s="14" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         </is>
       </c>
       <c r="H336" s="11" t="n">
-        <v>1.5</v>
+        <v>0.85</v>
       </c>
       <c r="I336" s="11" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         </is>
       </c>
       <c r="H337" s="14" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="I337" s="14" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="H338" s="11" t="n">
-        <v>2.11</v>
+        <v>0.52</v>
       </c>
       <c r="I338" s="11" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         </is>
       </c>
       <c r="H339" s="14" t="n">
-        <v>0.85</v>
+        <v>1.9</v>
       </c>
       <c r="I339" s="14" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         </is>
       </c>
       <c r="H340" s="11" t="n">
-        <v>1.1</v>
+        <v>2.27</v>
       </c>
       <c r="I340" s="11" t="inlineStr">
         <is>
@@ -17807,7 +17807,7 @@
         </is>
       </c>
       <c r="H341" s="14" t="n">
-        <v>2.28</v>
+        <v>1</v>
       </c>
       <c r="I341" s="14" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         </is>
       </c>
       <c r="H342" s="11" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="I342" s="11" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         </is>
       </c>
       <c r="H343" s="14" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="I343" s="14" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         </is>
       </c>
       <c r="H344" s="11" t="n">
-        <v>0.6</v>
+        <v>1.54</v>
       </c>
       <c r="I344" s="11" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="H345" s="14" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="I345" s="14" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         </is>
       </c>
       <c r="H346" s="11" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="I346" s="11" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         </is>
       </c>
       <c r="H347" s="14" t="n">
-        <v>1.88</v>
+        <v>1.15</v>
       </c>
       <c r="I347" s="14" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         </is>
       </c>
       <c r="H348" s="11" t="n">
-        <v>1.83</v>
+        <v>0.75</v>
       </c>
       <c r="I348" s="11" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         </is>
       </c>
       <c r="H349" s="14" t="n">
-        <v>2.33</v>
+        <v>1.58</v>
       </c>
       <c r="I349" s="14" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         </is>
       </c>
       <c r="H350" s="11" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="I350" s="11" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="H351" s="14" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="I351" s="14" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         </is>
       </c>
       <c r="H352" s="11" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="I352" s="11" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         </is>
       </c>
       <c r="H353" s="14" t="n">
-        <v>2.22</v>
+        <v>0.87</v>
       </c>
       <c r="I353" s="14" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         </is>
       </c>
       <c r="H354" s="11" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="I354" s="11" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="H355" s="14" t="n">
-        <v>1.01</v>
+        <v>2.17</v>
       </c>
       <c r="I355" s="14" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         </is>
       </c>
       <c r="H356" s="11" t="n">
-        <v>2.08</v>
+        <v>1.2</v>
       </c>
       <c r="I356" s="11" t="inlineStr">
         <is>
@@ -18607,7 +18607,7 @@
         </is>
       </c>
       <c r="H357" s="14" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="I357" s="14" t="inlineStr">
         <is>
@@ -18657,7 +18657,7 @@
         </is>
       </c>
       <c r="H358" s="11" t="n">
-        <v>2.45</v>
+        <v>0.97</v>
       </c>
       <c r="I358" s="11" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         </is>
       </c>
       <c r="H359" s="14" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="I359" s="14" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         </is>
       </c>
       <c r="H360" s="11" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="I360" s="11" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         </is>
       </c>
       <c r="H361" s="14" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="I361" s="14" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         </is>
       </c>
       <c r="H362" s="11" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I362" s="11" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         </is>
       </c>
       <c r="H363" s="14" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="I363" s="14" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         </is>
       </c>
       <c r="H364" s="11" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="I364" s="11" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         </is>
       </c>
       <c r="H365" s="14" t="n">
-        <v>1.52</v>
+        <v>0.57</v>
       </c>
       <c r="I365" s="14" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="H366" s="11" t="n">
-        <v>0.64</v>
+        <v>2.3</v>
       </c>
       <c r="I366" s="11" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         </is>
       </c>
       <c r="H367" s="14" t="n">
-        <v>0.83</v>
+        <v>2.37</v>
       </c>
       <c r="I367" s="14" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         </is>
       </c>
       <c r="H368" s="11" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="I368" s="11" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         </is>
       </c>
       <c r="H369" s="14" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="I369" s="14" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         </is>
       </c>
       <c r="H370" s="11" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="I370" s="11" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         </is>
       </c>
       <c r="H371" s="14" t="n">
-        <v>0.42</v>
+        <v>2.28</v>
       </c>
       <c r="I371" s="14" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="H372" s="11" t="n">
-        <v>0.93</v>
+        <v>0.48</v>
       </c>
       <c r="I372" s="11" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         </is>
       </c>
       <c r="H373" s="14" t="n">
-        <v>2.49</v>
+        <v>0.49</v>
       </c>
       <c r="I373" s="14" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         </is>
       </c>
       <c r="H374" s="11" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="I374" s="11" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         </is>
       </c>
       <c r="H375" s="14" t="n">
-        <v>0.87</v>
+        <v>1.57</v>
       </c>
       <c r="I375" s="14" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         </is>
       </c>
       <c r="H376" s="11" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I376" s="11" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="H377" s="14" t="n">
-        <v>0.49</v>
+        <v>1.85</v>
       </c>
       <c r="I377" s="14" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="H378" s="11" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="I378" s="11" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="H379" s="14" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="I379" s="14" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         </is>
       </c>
       <c r="H380" s="11" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="I380" s="11" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="H381" s="14" t="n">
-        <v>0.6</v>
+        <v>2.03</v>
       </c>
       <c r="I381" s="14" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="H382" s="11" t="n">
-        <v>1.28</v>
+        <v>2.23</v>
       </c>
       <c r="I382" s="11" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         </is>
       </c>
       <c r="H383" s="14" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="I383" s="14" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         </is>
       </c>
       <c r="H384" s="11" t="n">
-        <v>1.44</v>
+        <v>0.84</v>
       </c>
       <c r="I384" s="11" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="H385" s="14" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="I385" s="14" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         </is>
       </c>
       <c r="H386" s="11" t="n">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="I386" s="11" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         </is>
       </c>
       <c r="H387" s="14" t="n">
-        <v>0.92</v>
+        <v>1.81</v>
       </c>
       <c r="I387" s="14" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         </is>
       </c>
       <c r="H388" s="11" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="I388" s="11" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         </is>
       </c>
       <c r="H389" s="14" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="I389" s="14" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         </is>
       </c>
       <c r="H390" s="11" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="I390" s="11" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         </is>
       </c>
       <c r="H391" s="14" t="n">
-        <v>2.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I391" s="14" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         </is>
       </c>
       <c r="H392" s="11" t="n">
-        <v>1.43</v>
+        <v>0.71</v>
       </c>
       <c r="I392" s="11" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         </is>
       </c>
       <c r="H393" s="14" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="I393" s="14" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         </is>
       </c>
       <c r="H394" s="11" t="n">
-        <v>0.84</v>
+        <v>1.52</v>
       </c>
       <c r="I394" s="11" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="H395" s="14" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="I395" s="14" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         </is>
       </c>
       <c r="H396" s="11" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="I396" s="11" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         </is>
       </c>
       <c r="H397" s="14" t="n">
-        <v>0.67</v>
+        <v>2.02</v>
       </c>
       <c r="I397" s="14" t="inlineStr">
         <is>
@@ -20657,7 +20657,7 @@
         </is>
       </c>
       <c r="H398" s="11" t="n">
-        <v>1.97</v>
+        <v>0.4</v>
       </c>
       <c r="I398" s="11" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="H399" s="14" t="n">
-        <v>2.07</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I399" s="14" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         </is>
       </c>
       <c r="H400" s="11" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="I400" s="11" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         </is>
       </c>
       <c r="H401" s="14" t="n">
-        <v>0.91</v>
+        <v>2.27</v>
       </c>
       <c r="I401" s="14" t="inlineStr">
         <is>
@@ -20857,7 +20857,7 @@
         </is>
       </c>
       <c r="H402" s="11" t="n">
-        <v>2.11</v>
+        <v>1.1</v>
       </c>
       <c r="I402" s="11" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         </is>
       </c>
       <c r="H403" s="14" t="n">
-        <v>2.19</v>
+        <v>0.6</v>
       </c>
       <c r="I403" s="14" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="H404" s="11" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="I404" s="11" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="H405" s="14" t="n">
-        <v>1.75</v>
+        <v>0.96</v>
       </c>
       <c r="I405" s="14" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         </is>
       </c>
       <c r="H406" s="11" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="I406" s="11" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         </is>
       </c>
       <c r="H407" s="14" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="I407" s="14" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="H408" s="11" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="I408" s="11" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         </is>
       </c>
       <c r="H409" s="14" t="n">
-        <v>0.48</v>
+        <v>1.31</v>
       </c>
       <c r="I409" s="14" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         </is>
       </c>
       <c r="H410" s="11" t="n">
-        <v>0.48</v>
+        <v>1.57</v>
       </c>
       <c r="I410" s="11" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="H411" s="14" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="I411" s="14" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="H412" s="11" t="n">
-        <v>2.25</v>
+        <v>0.97</v>
       </c>
       <c r="I412" s="11" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         </is>
       </c>
       <c r="H413" s="14" t="n">
-        <v>2.44</v>
+        <v>0.55</v>
       </c>
       <c r="I413" s="14" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         </is>
       </c>
       <c r="H414" s="11" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="I414" s="11" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         </is>
       </c>
       <c r="H415" s="14" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="I415" s="14" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="H416" s="11" t="n">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="I416" s="11" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         </is>
       </c>
       <c r="H417" s="14" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="I417" s="14" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         </is>
       </c>
       <c r="H418" s="11" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="I418" s="11" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         </is>
       </c>
       <c r="H419" s="14" t="n">
-        <v>0.6</v>
+        <v>1.92</v>
       </c>
       <c r="I419" s="14" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="H420" s="11" t="n">
-        <v>1.34</v>
+        <v>0.92</v>
       </c>
       <c r="I420" s="11" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         </is>
       </c>
       <c r="H421" s="14" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="I421" s="14" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         </is>
       </c>
       <c r="H422" s="11" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="I422" s="11" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         </is>
       </c>
       <c r="H423" s="14" t="n">
-        <v>0.63</v>
+        <v>1.62</v>
       </c>
       <c r="I423" s="14" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         </is>
       </c>
       <c r="H424" s="11" t="n">
-        <v>2.43</v>
+        <v>0.86</v>
       </c>
       <c r="I424" s="11" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         </is>
       </c>
       <c r="H425" s="14" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I425" s="14" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         </is>
       </c>
       <c r="H426" s="11" t="n">
-        <v>2.01</v>
+        <v>0.61</v>
       </c>
       <c r="I426" s="11" t="inlineStr">
         <is>
@@ -22107,7 +22107,7 @@
         </is>
       </c>
       <c r="H427" s="14" t="n">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="I427" s="14" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
         </is>
       </c>
       <c r="H428" s="11" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="I428" s="11" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         </is>
       </c>
       <c r="H429" s="14" t="n">
-        <v>1.19</v>
+        <v>2.5</v>
       </c>
       <c r="I429" s="14" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="H430" s="11" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="I430" s="11" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         </is>
       </c>
       <c r="H431" s="14" t="n">
-        <v>0.96</v>
+        <v>2.38</v>
       </c>
       <c r="I431" s="14" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="H432" s="11" t="n">
-        <v>1.42</v>
+        <v>0.6</v>
       </c>
       <c r="I432" s="11" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="H433" s="14" t="n">
-        <v>1.07</v>
+        <v>1.67</v>
       </c>
       <c r="I433" s="14" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
         </is>
       </c>
       <c r="H434" s="11" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="I434" s="11" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         </is>
       </c>
       <c r="H435" s="14" t="n">
-        <v>2.15</v>
+        <v>0.95</v>
       </c>
       <c r="I435" s="14" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         </is>
       </c>
       <c r="H436" s="11" t="n">
-        <v>0.41</v>
+        <v>2.43</v>
       </c>
       <c r="I436" s="11" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         </is>
       </c>
       <c r="H437" s="14" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="I437" s="14" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         </is>
       </c>
       <c r="H438" s="11" t="n">
-        <v>1.49</v>
+        <v>0.74</v>
       </c>
       <c r="I438" s="11" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         </is>
       </c>
       <c r="H439" s="14" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="I439" s="14" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         </is>
       </c>
       <c r="H440" s="11" t="n">
-        <v>0.65</v>
+        <v>1.27</v>
       </c>
       <c r="I440" s="11" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         </is>
       </c>
       <c r="H441" s="14" t="n">
-        <v>0.55</v>
+        <v>2.43</v>
       </c>
       <c r="I441" s="14" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         </is>
       </c>
       <c r="H442" s="11" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I442" s="11" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         </is>
       </c>
       <c r="H443" s="14" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="I443" s="14" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         </is>
       </c>
       <c r="H444" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="I444" s="11" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="H445" s="14" t="n">
-        <v>2.24</v>
+        <v>0.6</v>
       </c>
       <c r="I445" s="14" t="inlineStr">
         <is>
@@ -23057,7 +23057,7 @@
         </is>
       </c>
       <c r="H446" s="11" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="I446" s="11" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         </is>
       </c>
       <c r="H447" s="14" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="I447" s="14" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         </is>
       </c>
       <c r="H448" s="11" t="n">
-        <v>2.11</v>
+        <v>1.33</v>
       </c>
       <c r="I448" s="11" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         </is>
       </c>
       <c r="H449" s="14" t="n">
-        <v>0.43</v>
+        <v>1.02</v>
       </c>
       <c r="I449" s="14" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="H450" s="11" t="n">
-        <v>1.49</v>
+        <v>0.49</v>
       </c>
       <c r="I450" s="11" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         </is>
       </c>
       <c r="H451" s="14" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="I451" s="14" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="H452" s="11" t="n">
-        <v>1.51</v>
+        <v>0.91</v>
       </c>
       <c r="I452" s="11" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="H453" s="14" t="n">
-        <v>1.72</v>
+        <v>0.55</v>
       </c>
       <c r="I453" s="14" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         </is>
       </c>
       <c r="H454" s="11" t="n">
-        <v>1.18</v>
+        <v>0.7</v>
       </c>
       <c r="I454" s="11" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         </is>
       </c>
       <c r="H455" s="14" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="I455" s="14" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         </is>
       </c>
       <c r="H456" s="11" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="I456" s="11" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         </is>
       </c>
       <c r="H457" s="14" t="n">
-        <v>1.66</v>
+        <v>0.42</v>
       </c>
       <c r="I457" s="14" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         </is>
       </c>
       <c r="H458" s="11" t="n">
-        <v>2.17</v>
+        <v>1.05</v>
       </c>
       <c r="I458" s="11" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         </is>
       </c>
       <c r="H459" s="14" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="I459" s="14" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="H460" s="11" t="n">
-        <v>1.08</v>
+        <v>2.45</v>
       </c>
       <c r="I460" s="11" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         </is>
       </c>
       <c r="H461" s="14" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="I461" s="14" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         </is>
       </c>
       <c r="H462" s="11" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="I462" s="11" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         </is>
       </c>
       <c r="H463" s="14" t="n">
-        <v>2.19</v>
+        <v>1.02</v>
       </c>
       <c r="I463" s="14" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         </is>
       </c>
       <c r="H464" s="11" t="n">
-        <v>0.52</v>
+        <v>2.43</v>
       </c>
       <c r="I464" s="11" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="H465" s="14" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="I465" s="14" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         </is>
       </c>
       <c r="H466" s="11" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="I466" s="11" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="H467" s="14" t="n">
-        <v>1.2</v>
+        <v>0.82</v>
       </c>
       <c r="I467" s="14" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         </is>
       </c>
       <c r="H468" s="11" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="I468" s="11" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         </is>
       </c>
       <c r="H469" s="14" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="I469" s="14" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         </is>
       </c>
       <c r="H470" s="11" t="n">
-        <v>0.68</v>
+        <v>1.39</v>
       </c>
       <c r="I470" s="11" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         </is>
       </c>
       <c r="H471" s="14" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="I471" s="14" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         </is>
       </c>
       <c r="H2" s="17" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="I2" s="17" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0.41</v>
+        <v>1.83</v>
       </c>
       <c r="I3" s="18" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         </is>
       </c>
       <c r="H4" s="17" t="n">
-        <v>1.58</v>
+        <v>2.37</v>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         </is>
       </c>
       <c r="H5" s="18" t="n">
-        <v>2.49</v>
+        <v>1.12</v>
       </c>
       <c r="I5" s="18" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         </is>
       </c>
       <c r="H6" s="17" t="n">
-        <v>0.41</v>
+        <v>1.26</v>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         </is>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="I7" s="18" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         </is>
       </c>
       <c r="H8" s="17" t="n">
-        <v>2.43</v>
+        <v>0.76</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         </is>
       </c>
       <c r="H9" s="18" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         </is>
       </c>
       <c r="H10" s="17" t="n">
-        <v>1.21</v>
+        <v>2.16</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         </is>
       </c>
       <c r="H11" s="18" t="n">
-        <v>0.6</v>
+        <v>1.89</v>
       </c>
       <c r="I11" s="18" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         </is>
       </c>
       <c r="H12" s="17" t="n">
-        <v>0.86</v>
+        <v>1.56</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         </is>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.95</v>
+        <v>1.16</v>
       </c>
       <c r="I13" s="18" t="inlineStr">
         <is>
@@ -25035,7 +25035,7 @@
         </is>
       </c>
       <c r="H14" s="17" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="H15" s="18" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="I15" s="18" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         </is>
       </c>
       <c r="H16" s="17" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         </is>
       </c>
       <c r="H17" s="18" t="n">
-        <v>1.69</v>
+        <v>0.64</v>
       </c>
       <c r="I17" s="18" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         </is>
       </c>
       <c r="H18" s="17" t="n">
-        <v>1.05</v>
+        <v>0.64</v>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         </is>
       </c>
       <c r="H19" s="18" t="n">
-        <v>2.42</v>
+        <v>0.46</v>
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="H20" s="17" t="n">
-        <v>0.99</v>
+        <v>1.39</v>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         </is>
       </c>
       <c r="H21" s="18" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
@@ -25435,7 +25435,7 @@
         </is>
       </c>
       <c r="H22" s="17" t="n">
-        <v>1.51</v>
+        <v>0.41</v>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         </is>
       </c>
       <c r="H23" s="18" t="n">
-        <v>1.21</v>
+        <v>0.99</v>
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         </is>
       </c>
       <c r="H24" s="17" t="n">
-        <v>0.62</v>
+        <v>2.26</v>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0.85</v>
+        <v>0.99</v>
       </c>
       <c r="I25" s="18" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         </is>
       </c>
       <c r="H26" s="17" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         </is>
       </c>
       <c r="H27" s="18" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="I27" s="18" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         </is>
       </c>
       <c r="H28" s="17" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         </is>
       </c>
       <c r="H29" s="18" t="n">
-        <v>2.13</v>
+        <v>0.65</v>
       </c>
       <c r="I29" s="18" t="inlineStr">
         <is>
@@ -25835,7 +25835,7 @@
         </is>
       </c>
       <c r="H30" s="17" t="n">
-        <v>2.25</v>
+        <v>1.13</v>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="H31" s="18" t="n">
-        <v>0.79</v>
+        <v>1.92</v>
       </c>
       <c r="I31" s="18" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         </is>
       </c>
       <c r="H32" s="17" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         </is>
       </c>
       <c r="H33" s="18" t="n">
-        <v>2.1</v>
+        <v>0.42</v>
       </c>
       <c r="I33" s="18" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         </is>
       </c>
       <c r="H34" s="17" t="n">
-        <v>0.92</v>
+        <v>1.93</v>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         </is>
       </c>
       <c r="H35" s="18" t="n">
-        <v>0.71</v>
+        <v>0.44</v>
       </c>
       <c r="I35" s="18" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         </is>
       </c>
       <c r="H36" s="17" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="H37" s="18" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="I37" s="18" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         </is>
       </c>
       <c r="H38" s="17" t="n">
-        <v>1.04</v>
+        <v>0.99</v>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         </is>
       </c>
       <c r="H39" s="18" t="n">
-        <v>2.47</v>
+        <v>1.91</v>
       </c>
       <c r="I39" s="18" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         </is>
       </c>
       <c r="H40" s="17" t="n">
-        <v>1.44</v>
+        <v>0.89</v>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         </is>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="I41" s="18" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         </is>
       </c>
       <c r="H42" s="17" t="n">
-        <v>0.86</v>
+        <v>1.48</v>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         </is>
       </c>
       <c r="H43" s="18" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="I43" s="18" t="inlineStr">
         <is>
@@ -26535,7 +26535,7 @@
         </is>
       </c>
       <c r="H44" s="17" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         </is>
       </c>
       <c r="H45" s="18" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         </is>
       </c>
       <c r="H46" s="17" t="n">
-        <v>0.61</v>
+        <v>2.27</v>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="H47" s="18" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         </is>
       </c>
       <c r="H48" s="17" t="n">
-        <v>1.29</v>
+        <v>0.48</v>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="H49" s="18" t="n">
-        <v>1.53</v>
+        <v>0.48</v>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         </is>
       </c>
       <c r="H50" s="17" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         </is>
       </c>
       <c r="H51" s="18" t="n">
-        <v>1.04</v>
+        <v>0.46</v>
       </c>
       <c r="I51" s="18" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         </is>
       </c>
       <c r="H53" s="18" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="I53" s="18" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         </is>
       </c>
       <c r="H54" s="17" t="n">
-        <v>1.45</v>
+        <v>0.49</v>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         </is>
       </c>
       <c r="H55" s="18" t="n">
-        <v>1.81</v>
+        <v>0.95</v>
       </c>
       <c r="I55" s="18" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
         </is>
       </c>
       <c r="H56" s="17" t="n">
-        <v>0.63</v>
+        <v>2.31</v>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         </is>
       </c>
       <c r="H57" s="18" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="I57" s="18" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         </is>
       </c>
       <c r="H58" s="17" t="n">
-        <v>0.73</v>
+        <v>2.06</v>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         </is>
       </c>
       <c r="H59" s="18" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="I59" s="18" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         </is>
       </c>
       <c r="H60" s="17" t="n">
-        <v>1.38</v>
+        <v>0.83</v>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         </is>
       </c>
       <c r="H61" s="18" t="n">
-        <v>1.69</v>
+        <v>2.07</v>
       </c>
       <c r="I61" s="18" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         </is>
       </c>
       <c r="H62" s="17" t="n">
-        <v>1.06</v>
+        <v>2.42</v>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         </is>
       </c>
       <c r="H63" s="18" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="I63" s="18" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="H64" s="17" t="n">
-        <v>1.28</v>
+        <v>2.49</v>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="H65" s="18" t="n">
-        <v>2.38</v>
+        <v>1.49</v>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="H66" s="17" t="n">
-        <v>2.48</v>
+        <v>0.66</v>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="H67" s="18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="I67" s="18" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="H68" s="17" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="H69" s="18" t="n">
-        <v>1.2</v>
+        <v>2.19</v>
       </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="H70" s="17" t="n">
-        <v>2.19</v>
+        <v>0.89</v>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="H71" s="18" t="n">
-        <v>0.85</v>
+        <v>2.24</v>
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="H72" s="17" t="n">
-        <v>2.46</v>
+        <v>1.08</v>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         </is>
       </c>
       <c r="H73" s="18" t="n">
-        <v>0.63</v>
+        <v>1.77</v>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="H74" s="17" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="H75" s="18" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="H76" s="17" t="n">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="I76" s="17" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="H77" s="18" t="n">
-        <v>0.7</v>
+        <v>0.41</v>
       </c>
       <c r="I77" s="18" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="H78" s="17" t="n">
-        <v>2.29</v>
+        <v>0.58</v>
       </c>
       <c r="I78" s="17" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="H79" s="18" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="I79" s="18" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="H80" s="17" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="I80" s="17" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="H81" s="18" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="H82" s="17" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="I82" s="17" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="H83" s="18" t="n">
-        <v>0.42</v>
+        <v>2.41</v>
       </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="H84" s="17" t="n">
-        <v>0.57</v>
+        <v>1.4</v>
       </c>
       <c r="I84" s="17" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="H85" s="18" t="n">
-        <v>2.2</v>
+        <v>0.87</v>
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="H86" s="17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I86" s="17" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="H87" s="18" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="H88" s="17" t="n">
-        <v>0.87</v>
+        <v>1.7</v>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="H89" s="18" t="n">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="I89" s="18" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="H90" s="17" t="n">
-        <v>0.62</v>
+        <v>1.41</v>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="H91" s="18" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         </is>
       </c>
       <c r="H92" s="17" t="n">
-        <v>2.48</v>
+        <v>1.06</v>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         </is>
       </c>
       <c r="H93" s="18" t="n">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         </is>
       </c>
       <c r="H94" s="17" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         </is>
       </c>
       <c r="H95" s="18" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
@@ -29135,7 +29135,7 @@
         </is>
       </c>
       <c r="H96" s="17" t="n">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         </is>
       </c>
       <c r="H97" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         </is>
       </c>
       <c r="H98" s="17" t="n">
-        <v>0.59</v>
+        <v>1.73</v>
       </c>
       <c r="I98" s="17" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         </is>
       </c>
       <c r="H99" s="18" t="n">
-        <v>2.21</v>
+        <v>0.45</v>
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         </is>
       </c>
       <c r="H100" s="17" t="n">
-        <v>0.47</v>
+        <v>2.23</v>
       </c>
       <c r="I100" s="17" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="H101" s="18" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="I101" s="18" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         </is>
       </c>
       <c r="H102" s="17" t="n">
-        <v>0.64</v>
+        <v>1.4</v>
       </c>
       <c r="I102" s="17" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         </is>
       </c>
       <c r="H103" s="18" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         </is>
       </c>
       <c r="H104" s="17" t="n">
-        <v>1.65</v>
+        <v>0.89</v>
       </c>
       <c r="I104" s="17" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         </is>
       </c>
       <c r="H105" s="18" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         </is>
       </c>
       <c r="H106" s="17" t="n">
-        <v>2.3</v>
+        <v>0.41</v>
       </c>
       <c r="I106" s="17" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         </is>
       </c>
       <c r="H107" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="H108" s="17" t="n">
-        <v>0.54</v>
+        <v>1.8</v>
       </c>
       <c r="I108" s="17" t="inlineStr">
         <is>
@@ -29785,7 +29785,7 @@
         </is>
       </c>
       <c r="H109" s="18" t="n">
-        <v>2.26</v>
+        <v>1.38</v>
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         </is>
       </c>
       <c r="H110" s="17" t="n">
-        <v>1.24</v>
+        <v>0.4</v>
       </c>
       <c r="I110" s="17" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         </is>
       </c>
       <c r="H111" s="18" t="n">
-        <v>1.53</v>
+        <v>0.58</v>
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         </is>
       </c>
       <c r="H112" s="17" t="n">
-        <v>0.64</v>
+        <v>1.2</v>
       </c>
       <c r="I112" s="17" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         </is>
       </c>
       <c r="H113" s="18" t="n">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="I113" s="18" t="inlineStr">
         <is>
@@ -30035,7 +30035,7 @@
         </is>
       </c>
       <c r="H114" s="17" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="I114" s="17" t="inlineStr">
         <is>
@@ -30085,7 +30085,7 @@
         </is>
       </c>
       <c r="H115" s="18" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="I115" s="18" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="H116" s="17" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="I116" s="17" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         </is>
       </c>
       <c r="H117" s="18" t="n">
-        <v>0.64</v>
+        <v>1.02</v>
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         </is>
       </c>
       <c r="H118" s="17" t="n">
-        <v>1.61</v>
+        <v>1.02</v>
       </c>
       <c r="I118" s="17" t="inlineStr">
         <is>
@@ -30285,7 +30285,7 @@
         </is>
       </c>
       <c r="H119" s="18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         </is>
       </c>
       <c r="H120" s="17" t="n">
-        <v>1.89</v>
+        <v>0.55</v>
       </c>
       <c r="I120" s="17" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         </is>
       </c>
       <c r="H121" s="18" t="n">
-        <v>0.53</v>
+        <v>1.38</v>
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         </is>
       </c>
       <c r="H122" s="17" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="I122" s="17" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         </is>
       </c>
       <c r="H123" s="18" t="n">
-        <v>0.62</v>
+        <v>1.24</v>
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         </is>
       </c>
       <c r="H124" s="17" t="n">
-        <v>0.48</v>
+        <v>1.56</v>
       </c>
       <c r="I124" s="17" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="H125" s="18" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         </is>
       </c>
       <c r="H126" s="17" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="I126" s="17" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         </is>
       </c>
       <c r="H127" s="18" t="n">
-        <v>1.6</v>
+        <v>2.39</v>
       </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         </is>
       </c>
       <c r="H128" s="17" t="n">
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="I128" s="17" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         </is>
       </c>
       <c r="H129" s="18" t="n">
-        <v>2.39</v>
+        <v>0.82</v>
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         </is>
       </c>
       <c r="H130" s="17" t="n">
-        <v>0.96</v>
+        <v>1.65</v>
       </c>
       <c r="I130" s="17" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         </is>
       </c>
       <c r="H131" s="18" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="I131" s="18" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         </is>
       </c>
       <c r="H132" s="17" t="n">
-        <v>0.41</v>
+        <v>1.85</v>
       </c>
       <c r="I132" s="17" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         </is>
       </c>
       <c r="H133" s="18" t="n">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         </is>
       </c>
       <c r="H134" s="17" t="n">
-        <v>2.19</v>
+        <v>1.72</v>
       </c>
       <c r="I134" s="17" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         </is>
       </c>
       <c r="H135" s="18" t="n">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="I135" s="18" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         </is>
       </c>
       <c r="H136" s="17" t="n">
-        <v>2.41</v>
+        <v>0.75</v>
       </c>
       <c r="I136" s="17" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         </is>
       </c>
       <c r="H137" s="18" t="n">
-        <v>0.68</v>
+        <v>0.53</v>
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
@@ -31235,7 +31235,7 @@
         </is>
       </c>
       <c r="H138" s="17" t="n">
-        <v>2.26</v>
+        <v>0.54</v>
       </c>
       <c r="I138" s="17" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         </is>
       </c>
       <c r="H139" s="18" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         </is>
       </c>
       <c r="H140" s="17" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="I140" s="17" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         </is>
       </c>
       <c r="H141" s="18" t="n">
-        <v>0.62</v>
+        <v>2.37</v>
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="H142" s="17" t="n">
-        <v>2.21</v>
+        <v>1.05</v>
       </c>
       <c r="I142" s="17" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         </is>
       </c>
       <c r="H143" s="18" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
@@ -31535,7 +31535,7 @@
         </is>
       </c>
       <c r="H144" s="17" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="I144" s="17" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         </is>
       </c>
       <c r="H145" s="18" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         </is>
       </c>
       <c r="H146" s="17" t="n">
-        <v>2.01</v>
+        <v>0.74</v>
       </c>
       <c r="I146" s="17" t="inlineStr">
         <is>
@@ -31685,7 +31685,7 @@
         </is>
       </c>
       <c r="H147" s="18" t="n">
-        <v>0.43</v>
+        <v>2.09</v>
       </c>
       <c r="I147" s="18" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         </is>
       </c>
       <c r="H148" s="17" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="I148" s="17" t="inlineStr">
         <is>
@@ -31785,7 +31785,7 @@
         </is>
       </c>
       <c r="H149" s="18" t="n">
-        <v>1.31</v>
+        <v>0.41</v>
       </c>
       <c r="I149" s="18" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         </is>
       </c>
       <c r="H150" s="17" t="n">
-        <v>0.84</v>
+        <v>1.58</v>
       </c>
       <c r="I150" s="17" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         </is>
       </c>
       <c r="H151" s="18" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="I151" s="18" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         </is>
       </c>
       <c r="H152" s="17" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="I152" s="17" t="inlineStr">
         <is>
@@ -31985,7 +31985,7 @@
         </is>
       </c>
       <c r="H153" s="18" t="n">
-        <v>2.29</v>
+        <v>1.25</v>
       </c>
       <c r="I153" s="18" t="inlineStr">
         <is>
@@ -32035,7 +32035,7 @@
         </is>
       </c>
       <c r="H154" s="17" t="n">
-        <v>1.45</v>
+        <v>0.66</v>
       </c>
       <c r="I154" s="17" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
         </is>
       </c>
       <c r="H155" s="18" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="I155" s="18" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         </is>
       </c>
       <c r="H156" s="17" t="n">
-        <v>1.3</v>
+        <v>2.21</v>
       </c>
       <c r="I156" s="17" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         </is>
       </c>
       <c r="H157" s="18" t="n">
-        <v>2.36</v>
+        <v>1.16</v>
       </c>
       <c r="I157" s="18" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         </is>
       </c>
       <c r="H158" s="17" t="n">
-        <v>1.17</v>
+        <v>0.99</v>
       </c>
       <c r="I158" s="17" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         </is>
       </c>
       <c r="H159" s="18" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="I159" s="18" t="inlineStr">
         <is>
@@ -32335,7 +32335,7 @@
         </is>
       </c>
       <c r="H160" s="17" t="n">
-        <v>1.15</v>
+        <v>0.88</v>
       </c>
       <c r="I160" s="17" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         </is>
       </c>
       <c r="H161" s="18" t="n">
-        <v>0.78</v>
+        <v>1.18</v>
       </c>
       <c r="I161" s="18" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         </is>
       </c>
       <c r="H162" s="17" t="n">
-        <v>0.99</v>
+        <v>2.02</v>
       </c>
       <c r="I162" s="17" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         </is>
       </c>
       <c r="H163" s="18" t="n">
-        <v>0.53</v>
+        <v>1.3</v>
       </c>
       <c r="I163" s="18" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         </is>
       </c>
       <c r="H164" s="17" t="n">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
       <c r="I164" s="17" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         </is>
       </c>
       <c r="H165" s="18" t="n">
-        <v>1.96</v>
+        <v>1.19</v>
       </c>
       <c r="I165" s="18" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         </is>
       </c>
       <c r="H166" s="17" t="n">
-        <v>1.13</v>
+        <v>2.09</v>
       </c>
       <c r="I166" s="17" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         </is>
       </c>
       <c r="H167" s="18" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="I167" s="18" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         </is>
       </c>
       <c r="H168" s="17" t="n">
-        <v>1.65</v>
+        <v>0.54</v>
       </c>
       <c r="I168" s="17" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="H169" s="18" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="I169" s="18" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         </is>
       </c>
       <c r="H170" s="17" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="I170" s="17" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         </is>
       </c>
       <c r="H171" s="18" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="I171" s="18" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         </is>
       </c>
       <c r="H172" s="17" t="n">
-        <v>0.51</v>
+        <v>1.97</v>
       </c>
       <c r="I172" s="17" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         </is>
       </c>
       <c r="H173" s="18" t="n">
-        <v>1.1</v>
+        <v>2.29</v>
       </c>
       <c r="I173" s="18" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         </is>
       </c>
       <c r="H174" s="17" t="n">
-        <v>1.09</v>
+        <v>0.45</v>
       </c>
       <c r="I174" s="17" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         </is>
       </c>
       <c r="H175" s="18" t="n">
-        <v>0.66</v>
+        <v>1.31</v>
       </c>
       <c r="I175" s="18" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         </is>
       </c>
       <c r="H176" s="17" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="I176" s="17" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         </is>
       </c>
       <c r="H177" s="18" t="n">
-        <v>1.08</v>
+        <v>1.95</v>
       </c>
       <c r="I177" s="18" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         </is>
       </c>
       <c r="H178" s="17" t="n">
-        <v>1.96</v>
+        <v>1.15</v>
       </c>
       <c r="I178" s="17" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         </is>
       </c>
       <c r="H179" s="18" t="n">
-        <v>2.38</v>
+        <v>0.72</v>
       </c>
       <c r="I179" s="18" t="inlineStr">
         <is>
@@ -33335,7 +33335,7 @@
         </is>
       </c>
       <c r="H180" s="17" t="n">
-        <v>1.29</v>
+        <v>1.99</v>
       </c>
       <c r="I180" s="17" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         </is>
       </c>
       <c r="H181" s="18" t="n">
-        <v>0.96</v>
+        <v>1.83</v>
       </c>
       <c r="I181" s="18" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         </is>
       </c>
       <c r="H182" s="17" t="n">
-        <v>2.03</v>
+        <v>1.42</v>
       </c>
       <c r="I182" s="17" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         </is>
       </c>
       <c r="H183" s="18" t="n">
-        <v>0.63</v>
+        <v>1.62</v>
       </c>
       <c r="I183" s="18" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         </is>
       </c>
       <c r="H184" s="17" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="I184" s="17" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         </is>
       </c>
       <c r="H185" s="18" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="I185" s="18" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="H186" s="17" t="n">
-        <v>0.89</v>
+        <v>2.4</v>
       </c>
       <c r="I186" s="17" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         </is>
       </c>
       <c r="H187" s="18" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="I187" s="18" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         </is>
       </c>
       <c r="H188" s="17" t="n">
-        <v>0.97</v>
+        <v>1.84</v>
       </c>
       <c r="I188" s="17" t="inlineStr">
         <is>
@@ -33785,7 +33785,7 @@
         </is>
       </c>
       <c r="H189" s="18" t="n">
-        <v>1.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I189" s="18" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="H190" s="17" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="I190" s="17" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         </is>
       </c>
       <c r="H191" s="18" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="I191" s="18" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         </is>
       </c>
       <c r="H192" s="17" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="I192" s="17" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         </is>
       </c>
       <c r="H193" s="18" t="n">
-        <v>2.45</v>
+        <v>0.95</v>
       </c>
       <c r="I193" s="18" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         </is>
       </c>
       <c r="H194" s="17" t="n">
-        <v>1.17</v>
+        <v>2.26</v>
       </c>
       <c r="I194" s="17" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         </is>
       </c>
       <c r="H195" s="18" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="I195" s="18" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         </is>
       </c>
       <c r="H196" s="17" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="I196" s="17" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         </is>
       </c>
       <c r="H197" s="18" t="n">
-        <v>1.39</v>
+        <v>2.49</v>
       </c>
       <c r="I197" s="18" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         </is>
       </c>
       <c r="H198" s="17" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="I198" s="17" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         </is>
       </c>
       <c r="H199" s="18" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="I199" s="18" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         </is>
       </c>
       <c r="H200" s="17" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="I200" s="17" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         </is>
       </c>
       <c r="H201" s="18" t="n">
-        <v>0.61</v>
+        <v>1.94</v>
       </c>
       <c r="I201" s="18" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         </is>
       </c>
       <c r="H202" s="17" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="I202" s="17" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         </is>
       </c>
       <c r="H203" s="18" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="I203" s="18" t="inlineStr">
         <is>
@@ -34535,7 +34535,7 @@
         </is>
       </c>
       <c r="H204" s="17" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="I204" s="17" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         </is>
       </c>
       <c r="H205" s="18" t="n">
-        <v>0.74</v>
+        <v>0.98</v>
       </c>
       <c r="I205" s="18" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         </is>
       </c>
       <c r="H206" s="17" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="I206" s="17" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         </is>
       </c>
       <c r="H207" s="18" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="I207" s="18" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         </is>
       </c>
       <c r="H208" s="17" t="n">
-        <v>0.8</v>
+        <v>2.38</v>
       </c>
       <c r="I208" s="17" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         </is>
       </c>
       <c r="H209" s="18" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="I209" s="18" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         </is>
       </c>
       <c r="H210" s="17" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="I210" s="17" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         </is>
       </c>
       <c r="H211" s="18" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="I211" s="18" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="H212" s="17" t="n">
-        <v>0.44</v>
+        <v>1.86</v>
       </c>
       <c r="I212" s="17" t="inlineStr">
         <is>
@@ -34985,7 +34985,7 @@
         </is>
       </c>
       <c r="H213" s="18" t="n">
-        <v>0.87</v>
+        <v>2.16</v>
       </c>
       <c r="I213" s="18" t="inlineStr">
         <is>
@@ -35035,7 +35035,7 @@
         </is>
       </c>
       <c r="H214" s="17" t="n">
-        <v>1.37</v>
+        <v>1.95</v>
       </c>
       <c r="I214" s="17" t="inlineStr">
         <is>
@@ -35085,7 +35085,7 @@
         </is>
       </c>
       <c r="H215" s="18" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="I215" s="18" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         </is>
       </c>
       <c r="H216" s="17" t="n">
-        <v>0.65</v>
+        <v>2.18</v>
       </c>
       <c r="I216" s="17" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         </is>
       </c>
       <c r="H217" s="18" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="I217" s="18" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         </is>
       </c>
       <c r="H218" s="17" t="n">
-        <v>2.42</v>
+        <v>1.88</v>
       </c>
       <c r="I218" s="17" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         </is>
       </c>
       <c r="H219" s="18" t="n">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="I219" s="18" t="inlineStr">
         <is>
@@ -35335,7 +35335,7 @@
         </is>
       </c>
       <c r="H220" s="17" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="I220" s="17" t="inlineStr">
         <is>
@@ -35385,7 +35385,7 @@
         </is>
       </c>
       <c r="H221" s="18" t="n">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I221" s="18" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         </is>
       </c>
       <c r="H222" s="17" t="n">
-        <v>2.34</v>
+        <v>1.28</v>
       </c>
       <c r="I222" s="17" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         </is>
       </c>
       <c r="H223" s="18" t="n">
-        <v>1.77</v>
+        <v>0.59</v>
       </c>
       <c r="I223" s="18" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         </is>
       </c>
       <c r="H224" s="17" t="n">
-        <v>1.05</v>
+        <v>2.27</v>
       </c>
       <c r="I224" s="17" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         </is>
       </c>
       <c r="H225" s="18" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="I225" s="18" t="inlineStr">
         <is>
@@ -35635,7 +35635,7 @@
         </is>
       </c>
       <c r="H226" s="17" t="n">
-        <v>2.17</v>
+        <v>0.95</v>
       </c>
       <c r="I226" s="17" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         </is>
       </c>
       <c r="H227" s="18" t="n">
-        <v>0.92</v>
+        <v>1.43</v>
       </c>
       <c r="I227" s="18" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         </is>
       </c>
       <c r="H228" s="17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I228" s="17" t="inlineStr">
         <is>
@@ -35785,7 +35785,7 @@
         </is>
       </c>
       <c r="H229" s="18" t="n">
-        <v>1.41</v>
+        <v>0.91</v>
       </c>
       <c r="I229" s="18" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="H230" s="17" t="n">
-        <v>0.45</v>
+        <v>0.93</v>
       </c>
       <c r="I230" s="17" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         </is>
       </c>
       <c r="H231" s="18" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="I231" s="18" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         </is>
       </c>
       <c r="H232" s="17" t="n">
-        <v>1.89</v>
+        <v>1.02</v>
       </c>
       <c r="I232" s="17" t="inlineStr">
         <is>
@@ -35985,7 +35985,7 @@
         </is>
       </c>
       <c r="H233" s="18" t="n">
-        <v>0.7</v>
+        <v>1.87</v>
       </c>
       <c r="I233" s="18" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         </is>
       </c>
       <c r="H234" s="17" t="n">
-        <v>1.33</v>
+        <v>0.45</v>
       </c>
       <c r="I234" s="17" t="inlineStr">
         <is>
@@ -36085,7 +36085,7 @@
         </is>
       </c>
       <c r="H235" s="18" t="n">
-        <v>1.07</v>
+        <v>1.92</v>
       </c>
       <c r="I235" s="18" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         </is>
       </c>
       <c r="H236" s="17" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="I236" s="17" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         </is>
       </c>
       <c r="H237" s="18" t="n">
-        <v>1.43</v>
+        <v>2.36</v>
       </c>
       <c r="I237" s="18" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         </is>
       </c>
       <c r="H238" s="17" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="I238" s="17" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         </is>
       </c>
       <c r="H239" s="18" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="I239" s="18" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         </is>
       </c>
       <c r="H240" s="17" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="I240" s="17" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         </is>
       </c>
       <c r="H241" s="18" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="I241" s="18" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         </is>
       </c>
       <c r="H242" s="17" t="n">
-        <v>0.65</v>
+        <v>1.9</v>
       </c>
       <c r="I242" s="17" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         </is>
       </c>
       <c r="H243" s="18" t="n">
-        <v>2.47</v>
+        <v>1.74</v>
       </c>
       <c r="I243" s="18" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         </is>
       </c>
       <c r="H244" s="17" t="n">
-        <v>1.31</v>
+        <v>0.57</v>
       </c>
       <c r="I244" s="17" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         </is>
       </c>
       <c r="H245" s="18" t="n">
-        <v>1.54</v>
+        <v>0.7</v>
       </c>
       <c r="I245" s="18" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         </is>
       </c>
       <c r="H246" s="17" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="I246" s="17" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="H247" s="18" t="n">
-        <v>1.23</v>
+        <v>1.95</v>
       </c>
       <c r="I247" s="18" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         </is>
       </c>
       <c r="H248" s="17" t="n">
-        <v>2</v>
+        <v>0.83</v>
       </c>
       <c r="I248" s="17" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         </is>
       </c>
       <c r="H249" s="18" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="I249" s="18" t="inlineStr">
         <is>
@@ -36835,7 +36835,7 @@
         </is>
       </c>
       <c r="H250" s="17" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="I250" s="17" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         </is>
       </c>
       <c r="H251" s="18" t="n">
-        <v>1.22</v>
+        <v>1.78</v>
       </c>
       <c r="I251" s="18" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         </is>
       </c>
       <c r="H252" s="17" t="n">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="I252" s="17" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         </is>
       </c>
       <c r="H253" s="18" t="n">
-        <v>1.45</v>
+        <v>0.64</v>
       </c>
       <c r="I253" s="18" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         </is>
       </c>
       <c r="H254" s="17" t="n">
-        <v>1.1</v>
+        <v>1.56</v>
       </c>
       <c r="I254" s="17" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         </is>
       </c>
       <c r="H255" s="18" t="n">
-        <v>1.22</v>
+        <v>0.59</v>
       </c>
       <c r="I255" s="18" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         </is>
       </c>
       <c r="H256" s="17" t="n">
-        <v>2.31</v>
+        <v>1.11</v>
       </c>
       <c r="I256" s="17" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         </is>
       </c>
       <c r="H257" s="18" t="n">
-        <v>1.05</v>
+        <v>0.59</v>
       </c>
       <c r="I257" s="18" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         </is>
       </c>
       <c r="H258" s="17" t="n">
-        <v>0.42</v>
+        <v>0.77</v>
       </c>
       <c r="I258" s="17" t="inlineStr">
         <is>
@@ -37285,7 +37285,7 @@
         </is>
       </c>
       <c r="H259" s="18" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="I259" s="18" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         </is>
       </c>
       <c r="H260" s="17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="I260" s="17" t="inlineStr">
         <is>
@@ -37385,7 +37385,7 @@
         </is>
       </c>
       <c r="H261" s="18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="I261" s="18" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         </is>
       </c>
       <c r="H262" s="17" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="I262" s="17" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         </is>
       </c>
       <c r="H263" s="18" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="I263" s="18" t="inlineStr">
         <is>
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="H264" s="17" t="n">
-        <v>2.12</v>
+        <v>0.46</v>
       </c>
       <c r="I264" s="17" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         </is>
       </c>
       <c r="H265" s="18" t="n">
-        <v>0.66</v>
+        <v>1.89</v>
       </c>
       <c r="I265" s="18" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         </is>
       </c>
       <c r="H266" s="17" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="I266" s="17" t="inlineStr">
         <is>
@@ -37685,7 +37685,7 @@
         </is>
       </c>
       <c r="H267" s="18" t="n">
-        <v>1.69</v>
+        <v>0.92</v>
       </c>
       <c r="I267" s="18" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         </is>
       </c>
       <c r="H268" s="17" t="n">
-        <v>0.95</v>
+        <v>0.61</v>
       </c>
       <c r="I268" s="17" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         </is>
       </c>
       <c r="H269" s="18" t="n">
-        <v>0.79</v>
+        <v>1.61</v>
       </c>
       <c r="I269" s="18" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         </is>
       </c>
       <c r="H270" s="17" t="n">
-        <v>1.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I270" s="17" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         </is>
       </c>
       <c r="H271" s="18" t="n">
-        <v>1.51</v>
+        <v>0.73</v>
       </c>
       <c r="I271" s="18" t="inlineStr">
         <is>
@@ -37935,7 +37935,7 @@
         </is>
       </c>
       <c r="H272" s="17" t="n">
-        <v>0.51</v>
+        <v>2.38</v>
       </c>
       <c r="I272" s="17" t="inlineStr">
         <is>
@@ -37985,7 +37985,7 @@
         </is>
       </c>
       <c r="H273" s="18" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="I273" s="18" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         </is>
       </c>
       <c r="H274" s="17" t="n">
-        <v>1.68</v>
+        <v>0.45</v>
       </c>
       <c r="I274" s="17" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         </is>
       </c>
       <c r="H275" s="18" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="I275" s="18" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         </is>
       </c>
       <c r="H276" s="17" t="n">
-        <v>2.35</v>
+        <v>1.33</v>
       </c>
       <c r="I276" s="17" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         </is>
       </c>
       <c r="H277" s="18" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="I277" s="18" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         </is>
       </c>
       <c r="H278" s="17" t="n">
-        <v>1.69</v>
+        <v>0.78</v>
       </c>
       <c r="I278" s="17" t="inlineStr">
         <is>
@@ -38285,7 +38285,7 @@
         </is>
       </c>
       <c r="H279" s="18" t="n">
-        <v>0.78</v>
+        <v>1.58</v>
       </c>
       <c r="I279" s="18" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         </is>
       </c>
       <c r="H280" s="17" t="n">
-        <v>2.11</v>
+        <v>0.68</v>
       </c>
       <c r="I280" s="17" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         </is>
       </c>
       <c r="H281" s="18" t="n">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="I281" s="18" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         </is>
       </c>
       <c r="H282" s="17" t="n">
-        <v>0.62</v>
+        <v>0.87</v>
       </c>
       <c r="I282" s="17" t="inlineStr">
         <is>
@@ -38485,7 +38485,7 @@
         </is>
       </c>
       <c r="H283" s="18" t="n">
-        <v>2.03</v>
+        <v>1.03</v>
       </c>
       <c r="I283" s="18" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         </is>
       </c>
       <c r="H284" s="17" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I284" s="17" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         </is>
       </c>
       <c r="H285" s="18" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="I285" s="18" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         </is>
       </c>
       <c r="H286" s="17" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="I286" s="17" t="inlineStr">
         <is>
@@ -38685,7 +38685,7 @@
         </is>
       </c>
       <c r="H287" s="18" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="I287" s="18" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         </is>
       </c>
       <c r="H288" s="17" t="n">
-        <v>1.06</v>
+        <v>0.61</v>
       </c>
       <c r="I288" s="17" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         </is>
       </c>
       <c r="H289" s="18" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="I289" s="18" t="inlineStr">
         <is>
@@ -38835,7 +38835,7 @@
         </is>
       </c>
       <c r="H290" s="17" t="n">
-        <v>0.52</v>
+        <v>1.65</v>
       </c>
       <c r="I290" s="17" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="H291" s="18" t="n">
-        <v>0.57</v>
+        <v>1.19</v>
       </c>
       <c r="I291" s="18" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         </is>
       </c>
       <c r="H292" s="17" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="I292" s="17" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         </is>
       </c>
       <c r="H293" s="18" t="n">
-        <v>1.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I293" s="18" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         </is>
       </c>
       <c r="H294" s="17" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="I294" s="17" t="inlineStr">
         <is>
@@ -39085,7 +39085,7 @@
         </is>
       </c>
       <c r="H295" s="18" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="I295" s="18" t="inlineStr">
         <is>
@@ -39135,7 +39135,7 @@
         </is>
       </c>
       <c r="H296" s="17" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="I296" s="17" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         </is>
       </c>
       <c r="H297" s="18" t="n">
-        <v>1.06</v>
+        <v>0.86</v>
       </c>
       <c r="I297" s="18" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         </is>
       </c>
       <c r="H298" s="17" t="n">
-        <v>0.74</v>
+        <v>1.56</v>
       </c>
       <c r="I298" s="17" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         </is>
       </c>
       <c r="H299" s="18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I299" s="18" t="inlineStr">
         <is>
@@ -39335,7 +39335,7 @@
         </is>
       </c>
       <c r="H300" s="17" t="n">
-        <v>0.97</v>
+        <v>1.26</v>
       </c>
       <c r="I300" s="17" t="inlineStr">
         <is>
@@ -39385,7 +39385,7 @@
         </is>
       </c>
       <c r="H301" s="18" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="I301" s="18" t="inlineStr">
         <is>
@@ -39435,7 +39435,7 @@
         </is>
       </c>
       <c r="H302" s="17" t="n">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="I302" s="17" t="inlineStr">
         <is>
@@ -39485,7 +39485,7 @@
         </is>
       </c>
       <c r="H303" s="18" t="n">
-        <v>2.05</v>
+        <v>1.16</v>
       </c>
       <c r="I303" s="18" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         </is>
       </c>
       <c r="H304" s="17" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="I304" s="17" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         </is>
       </c>
       <c r="H305" s="18" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="I305" s="18" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         </is>
       </c>
       <c r="H306" s="17" t="n">
-        <v>1.4</v>
+        <v>0.67</v>
       </c>
       <c r="I306" s="17" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         </is>
       </c>
       <c r="H307" s="18" t="n">
-        <v>1.68</v>
+        <v>2.48</v>
       </c>
       <c r="I307" s="18" t="inlineStr">
         <is>
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="H308" s="17" t="n">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="I308" s="17" t="inlineStr">
         <is>
@@ -39785,7 +39785,7 @@
         </is>
       </c>
       <c r="H309" s="18" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="I309" s="18" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         </is>
       </c>
       <c r="H310" s="17" t="n">
-        <v>0.9</v>
+        <v>2.08</v>
       </c>
       <c r="I310" s="17" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         </is>
       </c>
       <c r="H311" s="18" t="n">
-        <v>1.53</v>
+        <v>0.63</v>
       </c>
       <c r="I311" s="18" t="inlineStr">
         <is>
@@ -39935,7 +39935,7 @@
         </is>
       </c>
       <c r="H312" s="17" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="I312" s="17" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         </is>
       </c>
       <c r="H313" s="18" t="n">
-        <v>0.49</v>
+        <v>2.05</v>
       </c>
       <c r="I313" s="18" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         </is>
       </c>
       <c r="H314" s="17" t="n">
-        <v>2.22</v>
+        <v>0.57</v>
       </c>
       <c r="I314" s="17" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         </is>
       </c>
       <c r="H315" s="18" t="n">
-        <v>1.93</v>
+        <v>0.73</v>
       </c>
       <c r="I315" s="18" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         </is>
       </c>
       <c r="H316" s="17" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="I316" s="17" t="inlineStr">
         <is>
@@ -40185,7 +40185,7 @@
         </is>
       </c>
       <c r="H317" s="18" t="n">
-        <v>2.26</v>
+        <v>1.69</v>
       </c>
       <c r="I317" s="18" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         </is>
       </c>
       <c r="H318" s="17" t="n">
-        <v>0.48</v>
+        <v>1.34</v>
       </c>
       <c r="I318" s="17" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         </is>
       </c>
       <c r="H319" s="18" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="I319" s="18" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         </is>
       </c>
       <c r="H320" s="17" t="n">
-        <v>1.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I320" s="17" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         </is>
       </c>
       <c r="H321" s="18" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="I321" s="18" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         </is>
       </c>
       <c r="H322" s="17" t="n">
-        <v>2.49</v>
+        <v>1.92</v>
       </c>
       <c r="I322" s="17" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         </is>
       </c>
       <c r="H323" s="18" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="I323" s="18" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         </is>
       </c>
       <c r="H324" s="17" t="n">
-        <v>1.63</v>
+        <v>0.93</v>
       </c>
       <c r="I324" s="17" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         </is>
       </c>
       <c r="H325" s="18" t="n">
-        <v>0.67</v>
+        <v>0.54</v>
       </c>
       <c r="I325" s="18" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         </is>
       </c>
       <c r="H326" s="17" t="n">
-        <v>0.54</v>
+        <v>2.02</v>
       </c>
       <c r="I326" s="17" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         </is>
       </c>
       <c r="H327" s="18" t="n">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="I327" s="18" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         </is>
       </c>
       <c r="H328" s="17" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="I328" s="17" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         </is>
       </c>
       <c r="H329" s="18" t="n">
-        <v>2.15</v>
+        <v>0.87</v>
       </c>
       <c r="I329" s="18" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         </is>
       </c>
       <c r="H330" s="17" t="n">
-        <v>0.55</v>
+        <v>1.51</v>
       </c>
       <c r="I330" s="17" t="inlineStr">
         <is>
@@ -40885,7 +40885,7 @@
         </is>
       </c>
       <c r="H331" s="18" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="I331" s="18" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         </is>
       </c>
       <c r="H332" s="17" t="n">
-        <v>1.19</v>
+        <v>2.26</v>
       </c>
       <c r="I332" s="17" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         </is>
       </c>
       <c r="H333" s="18" t="n">
-        <v>2.18</v>
+        <v>1.06</v>
       </c>
       <c r="I333" s="18" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         </is>
       </c>
       <c r="H334" s="17" t="n">
-        <v>1.5</v>
+        <v>0.85</v>
       </c>
       <c r="I334" s="17" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         </is>
       </c>
       <c r="H335" s="18" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="I335" s="18" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         </is>
       </c>
       <c r="H336" s="17" t="n">
-        <v>2.11</v>
+        <v>0.52</v>
       </c>
       <c r="I336" s="17" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         </is>
       </c>
       <c r="H337" s="18" t="n">
-        <v>0.85</v>
+        <v>1.9</v>
       </c>
       <c r="I337" s="18" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         </is>
       </c>
       <c r="H338" s="17" t="n">
-        <v>1.1</v>
+        <v>2.27</v>
       </c>
       <c r="I338" s="17" t="inlineStr">
         <is>
@@ -41285,7 +41285,7 @@
         </is>
       </c>
       <c r="H339" s="18" t="n">
-        <v>2.28</v>
+        <v>1</v>
       </c>
       <c r="I339" s="18" t="inlineStr">
         <is>
@@ -41335,7 +41335,7 @@
         </is>
       </c>
       <c r="H340" s="17" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="I340" s="17" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         </is>
       </c>
       <c r="H341" s="18" t="n">
-        <v>1.91</v>
+        <v>1.03</v>
       </c>
       <c r="I341" s="18" t="inlineStr">
         <is>
@@ -41435,7 +41435,7 @@
         </is>
       </c>
       <c r="H342" s="17" t="n">
-        <v>0.6</v>
+        <v>1.54</v>
       </c>
       <c r="I342" s="17" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         </is>
       </c>
       <c r="H343" s="18" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="I343" s="18" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         </is>
       </c>
       <c r="H344" s="17" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="I344" s="17" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         </is>
       </c>
       <c r="H345" s="18" t="n">
-        <v>1.88</v>
+        <v>1.15</v>
       </c>
       <c r="I345" s="18" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         </is>
       </c>
       <c r="H346" s="17" t="n">
-        <v>1.83</v>
+        <v>0.75</v>
       </c>
       <c r="I346" s="17" t="inlineStr">
         <is>
@@ -41685,7 +41685,7 @@
         </is>
       </c>
       <c r="H347" s="18" t="n">
-        <v>2.33</v>
+        <v>1.58</v>
       </c>
       <c r="I347" s="18" t="inlineStr">
         <is>
@@ -41735,7 +41735,7 @@
         </is>
       </c>
       <c r="H348" s="17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="I348" s="17" t="inlineStr">
         <is>
@@ -41785,7 +41785,7 @@
         </is>
       </c>
       <c r="H349" s="18" t="n">
-        <v>1.26</v>
+        <v>1.78</v>
       </c>
       <c r="I349" s="18" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         </is>
       </c>
       <c r="H350" s="17" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="I350" s="17" t="inlineStr">
         <is>
@@ -41885,7 +41885,7 @@
         </is>
       </c>
       <c r="H351" s="18" t="n">
-        <v>2.22</v>
+        <v>0.87</v>
       </c>
       <c r="I351" s="18" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="H352" s="17" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="I352" s="17" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         </is>
       </c>
       <c r="H353" s="18" t="n">
-        <v>1.01</v>
+        <v>2.17</v>
       </c>
       <c r="I353" s="18" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         </is>
       </c>
       <c r="H354" s="17" t="n">
-        <v>2.08</v>
+        <v>1.2</v>
       </c>
       <c r="I354" s="17" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         </is>
       </c>
       <c r="H355" s="18" t="n">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="I355" s="18" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         </is>
       </c>
       <c r="H356" s="17" t="n">
-        <v>2.45</v>
+        <v>0.97</v>
       </c>
       <c r="I356" s="17" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         </is>
       </c>
       <c r="H357" s="18" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="I357" s="18" t="inlineStr">
         <is>
@@ -42235,7 +42235,7 @@
         </is>
       </c>
       <c r="H358" s="17" t="n">
-        <v>2.23</v>
+        <v>2.44</v>
       </c>
       <c r="I358" s="17" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         </is>
       </c>
       <c r="H359" s="18" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="I359" s="18" t="inlineStr">
         <is>
@@ -42335,7 +42335,7 @@
         </is>
       </c>
       <c r="H360" s="17" t="n">
-        <v>0.72</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I360" s="17" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         </is>
       </c>
       <c r="H361" s="18" t="n">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="I361" s="18" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         </is>
       </c>
       <c r="H362" s="17" t="n">
-        <v>1.78</v>
+        <v>2.27</v>
       </c>
       <c r="I362" s="17" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         </is>
       </c>
       <c r="H363" s="18" t="n">
-        <v>1.52</v>
+        <v>0.57</v>
       </c>
       <c r="I363" s="18" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         </is>
       </c>
       <c r="H364" s="17" t="n">
-        <v>0.64</v>
+        <v>2.3</v>
       </c>
       <c r="I364" s="17" t="inlineStr">
         <is>
@@ -42585,7 +42585,7 @@
         </is>
       </c>
       <c r="H365" s="18" t="n">
-        <v>0.83</v>
+        <v>2.37</v>
       </c>
       <c r="I365" s="18" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         </is>
       </c>
       <c r="H366" s="17" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="I366" s="17" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         </is>
       </c>
       <c r="H367" s="18" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="I367" s="18" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         </is>
       </c>
       <c r="H368" s="17" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="I368" s="17" t="inlineStr">
         <is>
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="H369" s="18" t="n">
-        <v>0.42</v>
+        <v>2.28</v>
       </c>
       <c r="I369" s="18" t="inlineStr">
         <is>
@@ -42835,7 +42835,7 @@
         </is>
       </c>
       <c r="H370" s="17" t="n">
-        <v>0.93</v>
+        <v>0.48</v>
       </c>
       <c r="I370" s="17" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         </is>
       </c>
       <c r="H371" s="18" t="n">
-        <v>2.49</v>
+        <v>0.49</v>
       </c>
       <c r="I371" s="18" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         </is>
       </c>
       <c r="H372" s="17" t="n">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="I372" s="17" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         </is>
       </c>
       <c r="H373" s="18" t="n">
-        <v>0.87</v>
+        <v>1.57</v>
       </c>
       <c r="I373" s="18" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         </is>
       </c>
       <c r="H374" s="17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I374" s="17" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         </is>
       </c>
       <c r="H375" s="18" t="n">
-        <v>0.49</v>
+        <v>1.85</v>
       </c>
       <c r="I375" s="18" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         </is>
       </c>
       <c r="H376" s="17" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="I376" s="17" t="inlineStr">
         <is>
@@ -43185,7 +43185,7 @@
         </is>
       </c>
       <c r="H377" s="18" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="I377" s="18" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         </is>
       </c>
       <c r="H378" s="17" t="n">
-        <v>0.75</v>
+        <v>1.63</v>
       </c>
       <c r="I378" s="17" t="inlineStr">
         <is>
@@ -43285,7 +43285,7 @@
         </is>
       </c>
       <c r="H379" s="18" t="n">
-        <v>0.6</v>
+        <v>2.03</v>
       </c>
       <c r="I379" s="18" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         </is>
       </c>
       <c r="H380" s="17" t="n">
-        <v>1.28</v>
+        <v>2.23</v>
       </c>
       <c r="I380" s="17" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         </is>
       </c>
       <c r="H381" s="18" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="I381" s="18" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         </is>
       </c>
       <c r="H382" s="17" t="n">
-        <v>1.44</v>
+        <v>0.84</v>
       </c>
       <c r="I382" s="17" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         </is>
       </c>
       <c r="H383" s="18" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="I383" s="18" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         </is>
       </c>
       <c r="H384" s="17" t="n">
-        <v>1.4</v>
+        <v>2.48</v>
       </c>
       <c r="I384" s="17" t="inlineStr">
         <is>
@@ -43585,7 +43585,7 @@
         </is>
       </c>
       <c r="H385" s="18" t="n">
-        <v>0.92</v>
+        <v>1.81</v>
       </c>
       <c r="I385" s="18" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         </is>
       </c>
       <c r="H386" s="17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="I386" s="17" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         </is>
       </c>
       <c r="H387" s="18" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="I387" s="18" t="inlineStr">
         <is>
@@ -43735,7 +43735,7 @@
         </is>
       </c>
       <c r="H388" s="17" t="n">
-        <v>0.62</v>
+        <v>1.01</v>
       </c>
       <c r="I388" s="17" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         </is>
       </c>
       <c r="H389" s="18" t="n">
-        <v>2.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I389" s="18" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         </is>
       </c>
       <c r="H390" s="17" t="n">
-        <v>1.43</v>
+        <v>0.71</v>
       </c>
       <c r="I390" s="17" t="inlineStr">
         <is>
@@ -43885,7 +43885,7 @@
         </is>
       </c>
       <c r="H391" s="18" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="I391" s="18" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         </is>
       </c>
       <c r="H392" s="17" t="n">
-        <v>0.84</v>
+        <v>1.52</v>
       </c>
       <c r="I392" s="17" t="inlineStr">
         <is>
@@ -43985,7 +43985,7 @@
         </is>
       </c>
       <c r="H393" s="18" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="I393" s="18" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         </is>
       </c>
       <c r="H394" s="17" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="I394" s="17" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         </is>
       </c>
       <c r="H395" s="18" t="n">
-        <v>0.67</v>
+        <v>2.02</v>
       </c>
       <c r="I395" s="18" t="inlineStr">
         <is>
@@ -44135,7 +44135,7 @@
         </is>
       </c>
       <c r="H396" s="17" t="n">
-        <v>1.97</v>
+        <v>0.4</v>
       </c>
       <c r="I396" s="17" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         </is>
       </c>
       <c r="H397" s="18" t="n">
-        <v>2.07</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I397" s="18" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         </is>
       </c>
       <c r="H398" s="17" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="I398" s="17" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         </is>
       </c>
       <c r="H399" s="18" t="n">
-        <v>0.91</v>
+        <v>2.27</v>
       </c>
       <c r="I399" s="18" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         </is>
       </c>
       <c r="H400" s="17" t="n">
-        <v>2.11</v>
+        <v>1.1</v>
       </c>
       <c r="I400" s="17" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         </is>
       </c>
       <c r="H401" s="18" t="n">
-        <v>2.19</v>
+        <v>0.6</v>
       </c>
       <c r="I401" s="18" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         </is>
       </c>
       <c r="H402" s="17" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="I402" s="17" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         </is>
       </c>
       <c r="H403" s="18" t="n">
-        <v>1.75</v>
+        <v>0.96</v>
       </c>
       <c r="I403" s="18" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         </is>
       </c>
       <c r="H404" s="17" t="n">
-        <v>1.81</v>
+        <v>1.24</v>
       </c>
       <c r="I404" s="17" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         </is>
       </c>
       <c r="H405" s="18" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="I405" s="18" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         </is>
       </c>
       <c r="H406" s="17" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="I406" s="17" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         </is>
       </c>
       <c r="H407" s="18" t="n">
-        <v>0.48</v>
+        <v>1.31</v>
       </c>
       <c r="I407" s="18" t="inlineStr">
         <is>
@@ -44735,7 +44735,7 @@
         </is>
       </c>
       <c r="H408" s="17" t="n">
-        <v>0.48</v>
+        <v>1.57</v>
       </c>
       <c r="I408" s="17" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         </is>
       </c>
       <c r="H409" s="18" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="I409" s="18" t="inlineStr">
         <is>
@@ -44835,7 +44835,7 @@
         </is>
       </c>
       <c r="H410" s="17" t="n">
-        <v>2.25</v>
+        <v>0.97</v>
       </c>
       <c r="I410" s="17" t="inlineStr">
         <is>
@@ -44885,7 +44885,7 @@
         </is>
       </c>
       <c r="H411" s="18" t="n">
-        <v>2.44</v>
+        <v>0.55</v>
       </c>
       <c r="I411" s="18" t="inlineStr">
         <is>
@@ -44935,7 +44935,7 @@
         </is>
       </c>
       <c r="H412" s="17" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="I412" s="17" t="inlineStr">
         <is>
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="H413" s="18" t="n">
-        <v>2.14</v>
+        <v>1</v>
       </c>
       <c r="I413" s="18" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         </is>
       </c>
       <c r="H414" s="17" t="n">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="I414" s="17" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         </is>
       </c>
       <c r="H415" s="18" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="I415" s="18" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         </is>
       </c>
       <c r="H416" s="17" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="I416" s="17" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         </is>
       </c>
       <c r="H417" s="18" t="n">
-        <v>0.6</v>
+        <v>1.92</v>
       </c>
       <c r="I417" s="18" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         </is>
       </c>
       <c r="H418" s="17" t="n">
-        <v>1.34</v>
+        <v>0.92</v>
       </c>
       <c r="I418" s="17" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         </is>
       </c>
       <c r="H419" s="18" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="I419" s="18" t="inlineStr">
         <is>
@@ -45335,7 +45335,7 @@
         </is>
       </c>
       <c r="H420" s="17" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="I420" s="17" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         </is>
       </c>
       <c r="H421" s="18" t="n">
-        <v>0.63</v>
+        <v>1.62</v>
       </c>
       <c r="I421" s="18" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         </is>
       </c>
       <c r="H422" s="17" t="n">
-        <v>2.43</v>
+        <v>0.86</v>
       </c>
       <c r="I422" s="17" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         </is>
       </c>
       <c r="H423" s="18" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I423" s="18" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         </is>
       </c>
       <c r="H424" s="17" t="n">
-        <v>2.01</v>
+        <v>0.61</v>
       </c>
       <c r="I424" s="17" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         </is>
       </c>
       <c r="H425" s="18" t="n">
-        <v>0.6</v>
+        <v>1.16</v>
       </c>
       <c r="I425" s="18" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         </is>
       </c>
       <c r="H426" s="17" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="I426" s="17" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         </is>
       </c>
       <c r="H427" s="18" t="n">
-        <v>1.19</v>
+        <v>2.5</v>
       </c>
       <c r="I427" s="18" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         </is>
       </c>
       <c r="H428" s="17" t="n">
-        <v>0.67</v>
+        <v>1.46</v>
       </c>
       <c r="I428" s="17" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         </is>
       </c>
       <c r="H429" s="18" t="n">
-        <v>0.96</v>
+        <v>2.38</v>
       </c>
       <c r="I429" s="18" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="H430" s="17" t="n">
-        <v>1.42</v>
+        <v>0.6</v>
       </c>
       <c r="I430" s="17" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         </is>
       </c>
       <c r="H431" s="18" t="n">
-        <v>1.07</v>
+        <v>1.67</v>
       </c>
       <c r="I431" s="18" t="inlineStr">
         <is>
@@ -45935,7 +45935,7 @@
         </is>
       </c>
       <c r="H432" s="17" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="I432" s="17" t="inlineStr">
         <is>
@@ -45985,7 +45985,7 @@
         </is>
       </c>
       <c r="H433" s="18" t="n">
-        <v>2.15</v>
+        <v>0.95</v>
       </c>
       <c r="I433" s="18" t="inlineStr">
         <is>
@@ -46035,7 +46035,7 @@
         </is>
       </c>
       <c r="H434" s="17" t="n">
-        <v>0.41</v>
+        <v>2.43</v>
       </c>
       <c r="I434" s="17" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         </is>
       </c>
       <c r="H435" s="18" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="I435" s="18" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         </is>
       </c>
       <c r="H436" s="17" t="n">
-        <v>1.49</v>
+        <v>0.74</v>
       </c>
       <c r="I436" s="17" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         </is>
       </c>
       <c r="H437" s="18" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="I437" s="18" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         </is>
       </c>
       <c r="H438" s="17" t="n">
-        <v>0.65</v>
+        <v>1.27</v>
       </c>
       <c r="I438" s="17" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         </is>
       </c>
       <c r="H439" s="18" t="n">
-        <v>0.55</v>
+        <v>2.43</v>
       </c>
       <c r="I439" s="18" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         </is>
       </c>
       <c r="H440" s="17" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I440" s="17" t="inlineStr">
         <is>
@@ -46385,7 +46385,7 @@
         </is>
       </c>
       <c r="H441" s="18" t="n">
-        <v>2.39</v>
+        <v>1.96</v>
       </c>
       <c r="I441" s="18" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         </is>
       </c>
       <c r="H442" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="I442" s="17" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         </is>
       </c>
       <c r="H443" s="18" t="n">
-        <v>2.24</v>
+        <v>0.6</v>
       </c>
       <c r="I443" s="18" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         </is>
       </c>
       <c r="H444" s="17" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="I444" s="17" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         </is>
       </c>
       <c r="H445" s="18" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="I445" s="18" t="inlineStr">
         <is>
@@ -46635,7 +46635,7 @@
         </is>
       </c>
       <c r="H446" s="17" t="n">
-        <v>2.11</v>
+        <v>1.33</v>
       </c>
       <c r="I446" s="17" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         </is>
       </c>
       <c r="H447" s="18" t="n">
-        <v>0.43</v>
+        <v>1.02</v>
       </c>
       <c r="I447" s="18" t="inlineStr">
         <is>
@@ -46735,7 +46735,7 @@
         </is>
       </c>
       <c r="H448" s="17" t="n">
-        <v>1.49</v>
+        <v>0.49</v>
       </c>
       <c r="I448" s="17" t="inlineStr">
         <is>
@@ -46785,7 +46785,7 @@
         </is>
       </c>
       <c r="H449" s="18" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="I449" s="18" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         </is>
       </c>
       <c r="H450" s="17" t="n">
-        <v>1.51</v>
+        <v>0.91</v>
       </c>
       <c r="I450" s="17" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         </is>
       </c>
       <c r="H451" s="18" t="n">
-        <v>1.72</v>
+        <v>0.55</v>
       </c>
       <c r="I451" s="18" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         </is>
       </c>
       <c r="H452" s="17" t="n">
-        <v>1.18</v>
+        <v>0.7</v>
       </c>
       <c r="I452" s="17" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         </is>
       </c>
       <c r="H453" s="18" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="I453" s="18" t="inlineStr">
         <is>
@@ -47035,7 +47035,7 @@
         </is>
       </c>
       <c r="H454" s="17" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="I454" s="17" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         </is>
       </c>
       <c r="H455" s="18" t="n">
-        <v>1.66</v>
+        <v>0.42</v>
       </c>
       <c r="I455" s="18" t="inlineStr">
         <is>
@@ -47135,7 +47135,7 @@
         </is>
       </c>
       <c r="H456" s="17" t="n">
-        <v>2.17</v>
+        <v>1.05</v>
       </c>
       <c r="I456" s="17" t="inlineStr">
         <is>
@@ -47185,7 +47185,7 @@
         </is>
       </c>
       <c r="H457" s="18" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="I457" s="18" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         </is>
       </c>
       <c r="H458" s="17" t="n">
-        <v>1.08</v>
+        <v>2.45</v>
       </c>
       <c r="I458" s="17" t="inlineStr">
         <is>
@@ -47285,7 +47285,7 @@
         </is>
       </c>
       <c r="H459" s="18" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="I459" s="18" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         </is>
       </c>
       <c r="H460" s="17" t="n">
-        <v>2.11</v>
+        <v>1.76</v>
       </c>
       <c r="I460" s="17" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         </is>
       </c>
       <c r="H461" s="18" t="n">
-        <v>2.19</v>
+        <v>1.02</v>
       </c>
       <c r="I461" s="18" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         </is>
       </c>
       <c r="H462" s="17" t="n">
-        <v>0.52</v>
+        <v>2.43</v>
       </c>
       <c r="I462" s="17" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         </is>
       </c>
       <c r="H463" s="18" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="I463" s="18" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         </is>
       </c>
       <c r="H464" s="17" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="I464" s="17" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         </is>
       </c>
       <c r="H465" s="18" t="n">
-        <v>1.2</v>
+        <v>0.82</v>
       </c>
       <c r="I465" s="18" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         </is>
       </c>
       <c r="H466" s="17" t="n">
-        <v>1.25</v>
+        <v>1.96</v>
       </c>
       <c r="I466" s="17" t="inlineStr">
         <is>
@@ -47685,7 +47685,7 @@
         </is>
       </c>
       <c r="H467" s="18" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="I467" s="18" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         </is>
       </c>
       <c r="H468" s="17" t="n">
-        <v>0.68</v>
+        <v>1.39</v>
       </c>
       <c r="I468" s="17" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         </is>
       </c>
       <c r="H469" s="18" t="n">
-        <v>1.16</v>
+        <v>1.72</v>
       </c>
       <c r="I469" s="18" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         </is>
       </c>
       <c r="E2" s="17" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="F2" s="17" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         </is>
       </c>
       <c r="E3" s="18" t="n">
-        <v>2.49</v>
+        <v>0.5</v>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
